--- a/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>VZ</t>
   </si>
@@ -656,395 +656,407 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>35130000</v>
+      </c>
+      <c r="E8" s="3">
         <v>33336000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>32596000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>32912000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>35251000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>34241000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33789000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33554000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>34067000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32915000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33764000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>32867000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34692000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>31543000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>30447000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>31610000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34775000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>32894000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>32071000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>32128000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34281000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>32607000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>32203000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>31772000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>33955000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>31717000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>30548000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>29814000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>32340000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>30937000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>13437000</v>
+        <v>15174000</v>
       </c>
       <c r="E9" s="3">
-        <v>12764000</v>
+        <v>13377000</v>
       </c>
       <c r="F9" s="3">
+        <v>12750000</v>
+      </c>
+      <c r="G9" s="3">
         <v>13504000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15762000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14601000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14420000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14350000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14996000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13528000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14255000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13522000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14822000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12334000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>11749000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12296000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15631000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13384000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12721000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12990000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>15291000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>13331000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13328000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13255000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15387000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>20614000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12484000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12047000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>14362000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>12229000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>19899000</v>
+        <v>19956000</v>
       </c>
       <c r="E10" s="3">
-        <v>19832000</v>
+        <v>19959000</v>
       </c>
       <c r="F10" s="3">
+        <v>19846000</v>
+      </c>
+      <c r="G10" s="3">
         <v>19408000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19489000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19640000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19369000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19204000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19071000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19387000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19509000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19345000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19870000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19209000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>18698000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>19314000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19144000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19510000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19350000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19138000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>18990000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19276000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>18875000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>18517000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>18568000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>11103000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>18064000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>17767000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>17978000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>18708000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1089,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1169,8 +1182,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,192 +1277,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-85000</v>
+        <v>7470000</v>
       </c>
       <c r="E14" s="3">
-        <v>-306000</v>
+        <v>270000</v>
       </c>
       <c r="F14" s="3">
+        <v>323000</v>
+      </c>
+      <c r="G14" s="3">
         <v>-70000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2214000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>645000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>198000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1241000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1230000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>948000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-168000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>223000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>404000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1092000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>255000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1377000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2381000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>291000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1544000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-96000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>4945000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>159000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>910000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>356000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2558000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>620000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-1015000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>722000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-1589000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>797000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>4431000</v>
+        <v>4516000</v>
       </c>
       <c r="E15" s="3">
+        <v>4410000</v>
+      </c>
+      <c r="F15" s="3">
         <v>4359000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4318000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4218000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4324000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4321000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4236000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4051000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3961000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4020000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4174000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4197000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4192000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4181000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4150000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4105000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4114000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4232000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4231000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4350000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4370000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4338000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4322000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4237000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>8544000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>12388000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>8118000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>3987000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1476,192 +1501,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35438000</v>
+      </c>
+      <c r="E17" s="3">
         <v>25778000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25307000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25258000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25508000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>26992000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>26435000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>26999000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27689000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24958000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25431000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25097000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>27695000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24957000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23341000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25213000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>30127000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25005000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25765000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>24323000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>31991000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>24954000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>25586000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>24672000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>30058000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>25183000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>22534000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>23700000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>24317000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>24397000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-308000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7558000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7289000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7654000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9743000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7249000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7354000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6555000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6378000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7957000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8333000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7770000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6997000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6586000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7106000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6397000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4648000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7889000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6306000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7805000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2290000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7653000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6617000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7100000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3897000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>6534000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>8014000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>6114000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>8023000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6540000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1694,468 +1726,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E20" s="3">
         <v>67000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>108000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>53000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>173000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>208000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>288000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>314000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>505000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1218000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>335000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>409000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>336000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>309000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>197000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>313000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>223000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>180000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>219000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>193000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>276000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>233000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>132000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>155000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>256000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>141000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>171000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>200000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>63000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4298000</v>
+      </c>
+      <c r="E21" s="3">
         <v>12056000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11756000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12025000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14134000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11781000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11963000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11105000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10934000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13136000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12688000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12353000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11530000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11087000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11484000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>10860000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8976000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12183000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>10757000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12229000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6918000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>12263000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>11099000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11579000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>8609000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>10947000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>12352000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>10373000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>12073000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>10556000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1599000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1433000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1285000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1207000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1105000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>937000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>785000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>786000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>739000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>801000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>844000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1101000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1080000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1044000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1116000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1034000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1159000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1146000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1215000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1210000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1199000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1211000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1222000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1201000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1219000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1164000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1218000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1132000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1137000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1038000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1817000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6192000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6112000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6500000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8811000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6520000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6857000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6083000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6144000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8374000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7824000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7078000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6253000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5851000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6187000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5676000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3712000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6923000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5310000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6788000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1367000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6675000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5527000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6054000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2934000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5511000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6967000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5182000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6949000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5576000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>756000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1308000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1346000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1482000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2113000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1496000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1542000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1372000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1407000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1820000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1875000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1700000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1535000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1347000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1348000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1389000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1505000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1586000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1236000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1628000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-698000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1613000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1281000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1388000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>912000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1775000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2489000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1629000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2349000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1829000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,192 +2294,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2573000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4884000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4766000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5018000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6698000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5024000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5315000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4711000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4737000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6554000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5949000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5378000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4718000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4504000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4839000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4287000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5217000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5337000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4074000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5160000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2065000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5062000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4246000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4666000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2022000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3736000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4478000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3553000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4600000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3747000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2705000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4762000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4648000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4909000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6577000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4900000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5199000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4580000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4613000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6407000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5800000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5245000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4588000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4357000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4700000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4156000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5095000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5194000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3944000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5032000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1939000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4924000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4120000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4545000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1908000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3620000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4362000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3450000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4495000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2522,8 +2579,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2578,17 +2638,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
+      <c r="W29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2596,11 +2656,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>16761000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2614,8 +2674,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2706,8 +2769,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2798,192 +2864,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-67000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-108000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-53000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-173000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-208000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-288000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-314000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-505000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1218000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-335000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-409000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-336000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-309000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-197000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-313000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-223000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-180000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-219000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-193000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-276000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-233000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-132000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-256000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-171000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-200000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-63000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-74000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2705000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4762000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4648000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4909000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6577000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4900000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5199000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4580000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4613000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6407000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5800000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5245000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4588000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4357000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4700000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4156000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5095000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5194000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3944000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5032000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1939000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4924000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4120000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4545000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>18669000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3620000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4362000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3450000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4495000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3074,197 +3149,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2705000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4762000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4648000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4909000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6577000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4900000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5199000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4580000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4613000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6407000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5800000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5245000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4588000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4357000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4700000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4156000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5095000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5194000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3944000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5032000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1939000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4924000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4120000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4545000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>18669000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3620000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4362000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3450000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4495000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3297,8 +3381,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3331,100 +3416,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2065000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4210000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4803000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2234000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2605000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2082000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1857000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1661000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2921000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9936000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4657000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10205000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22171000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8983000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7882000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7047000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2594000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3020000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1949000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2322000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2745000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2538000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1750000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1923000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2079000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4487000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4583000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4307000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2880000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6441000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3515,652 +3604,676 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25631000</v>
+      </c>
+      <c r="E43" s="3">
         <v>23851000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>23728000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>23436000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>24506000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24362000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24606000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24335000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24585000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>22896000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>22029000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23236000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24650000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>23350000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>23434000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24641000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>26277000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>25531000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>25738000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>25239000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>25859000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>24765000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>23875000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>22595000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>23493000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>21549000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>19771000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>16863000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>17513000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>14832000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2057000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2240000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1896000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2381000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2388000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3133000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3646000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3659000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3055000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2303000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1421000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1303000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1796000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1457000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1289000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1633000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1422000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1538000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1167000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1417000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1336000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1270000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1102000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1285000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1276000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1116000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1194000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1202000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1318000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7061000</v>
+      </c>
+      <c r="E45" s="3">
         <v>7818000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6961000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7671000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8358000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10169000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7390000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5925000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6167000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5142000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7519000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4903000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5977000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4782000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4728000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7384000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7180000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4806000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4454000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4419000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4696000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4581000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4149000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5222000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3307000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3555000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3353000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4794000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4800000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3030000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>36814000</v>
+      </c>
+      <c r="E46" s="3">
         <v>38119000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>37388000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>35722000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>37857000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>39746000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37499000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>35580000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36728000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>40277000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>35626000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>39647000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>54594000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>38572000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>37333000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>40705000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>37473000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>34895000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>33308000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>33397000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>34636000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>33154000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>30876000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>31025000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>29913000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>30867000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>28823000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>27158000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>26395000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>25621000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1221000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1178000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1247000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1249000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1278000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1260000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1296000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1263000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1256000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1277000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>760000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>749000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>793000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>725000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>760000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>834000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>860000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>912000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>897000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>925000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>917000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>976000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1070000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>994000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1039000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1054000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1075000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1080000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1110000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1119000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>133036000</v>
+      </c>
+      <c r="E48" s="3">
         <v>132576000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>132615000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>132934000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>133564000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>129592000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>128408000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>127337000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>127579000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>123725000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>122382000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>117191000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>117364000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>115862000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>115185000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>114649000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>114609000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>111067000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>110285000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>110954000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>89286000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>87464000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>87781000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>87922000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>88568000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>86622000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>86521000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>85213000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>84751000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>83414000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>189567000</v>
+      </c>
+      <c r="E49" s="3">
         <v>195059000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>191081000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>190405000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>189928000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>189036000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>188648000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>188144000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>187899000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>177676000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>129951000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>132153000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>130283000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>130356000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>130034000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>126224000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>128946000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>128267000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>128439000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>128480000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>128519000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>132937000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>132916000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>132812000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>127836000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>127601000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>127674000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>124296000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>122775000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>121069000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4251,8 +4364,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4343,100 +4459,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>19617000</v>
+      </c>
+      <c r="E52" s="3">
         <v>17898000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>17624000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17406000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17053000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15456000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14296000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13392000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13134000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10502000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>60471000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>55833000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13447000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11479000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9947000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12088000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9839000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9734000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10179000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10191000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11471000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11031000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10660000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11763000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9787000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8538000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8885000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8984000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9149000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8275000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4527,100 +4649,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>380255000</v>
+      </c>
+      <c r="E54" s="3">
         <v>384830000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>379955000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>377716000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>379680000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>375090000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>370147000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>365716000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>366596000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>353457000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>349190000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>345573000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>316481000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>296994000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>293259000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>294500000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>291727000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>284875000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>283108000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>283947000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>264829000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>265562000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>263303000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>264516000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>257143000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>254682000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>252978000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>246731000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>244180000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>239498000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4653,8 +4781,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4687,560 +4816,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>23453000</v>
+      </c>
+      <c r="E57" s="3">
         <v>26140000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20067000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19273000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23977000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22235000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>20956000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18169000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24833000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>20153000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17328000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17219000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20658000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17391000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>19297000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17419000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>21806000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19566000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17633000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>18664000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>22501000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>19342000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>18560000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>17052000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>21232000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>18434000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>17825000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>14826000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>13876000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>18002000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12973000</v>
+      </c>
+      <c r="E58" s="3">
         <v>12950000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14827000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12081000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9963000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14995000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12873000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13421000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7443000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7623000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7023000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8802000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5889000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5770000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6651000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>11175000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>10777000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>7830000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>8773000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>8614000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7190000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6502000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5466000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6323000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3453000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2180000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1153000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3707000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2645000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3852000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16797000</v>
+      </c>
+      <c r="E59" s="3">
         <v>16587000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16510000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16414000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16231000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15911000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15395000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14995000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14884000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13582000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15727000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12709000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13113000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13024000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12938000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12463000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12285000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11813000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11808000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11329000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8239000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8323000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8303000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8240000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8352000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8316000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8780000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8131000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>13819000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8444000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53223000</v>
+      </c>
+      <c r="E60" s="3">
         <v>55677000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>51404000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>47768000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>50171000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53141000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>49224000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>46585000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>47160000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41358000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>40078000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>38730000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>39660000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>36185000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>38886000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>41057000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>44868000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>39209000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38214000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38607000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>37930000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>34167000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>32329000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>31615000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>33037000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>28930000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>27758000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>26664000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>30340000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>30298000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>137701000</v>
+      </c>
+      <c r="E61" s="3">
         <v>134441000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>137871000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>140772000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>140676000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>132912000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>136184000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>139961000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>143425000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>143352000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>144894000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>149700000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>123173000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>109790000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>106190000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>106561000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>100712000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>101769000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>104598000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>105045000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>105873000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>106440000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>109174000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>112734000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>113642000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>115317000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>116390000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>112839000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>105433000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>102739000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>95532000</v>
+      </c>
+      <c r="E62" s="3">
         <v>95624000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>94178000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>94957000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>96370000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>100254000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>97382000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>93995000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>92811000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>90258000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>89106000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>84460000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>84376000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>84489000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>84070000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>85229000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>83312000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>83585000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>82349000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>82835000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>66316000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>68868000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>68225000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>67822000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>65777000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>81984000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>82069000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>82191000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>84375000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>84478000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5331,8 +5479,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5423,8 +5574,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5515,100 +5669,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>287825000</v>
+      </c>
+      <c r="E66" s="3">
         <v>287089000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>284762000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>284833000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>288536000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>287622000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>284131000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>281954000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>284806000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>276413000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>275506000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>274341000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>248639000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>231925000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>230562000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>234290000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>230332000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>225954000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>226526000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>228091000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>211684000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>211067000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>211279000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>213735000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>214047000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>227834000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>227789000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>223238000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>221656000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>219038000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5641,8 +5801,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5733,8 +5894,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5825,8 +5989,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5917,8 +6084,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6009,100 +6179,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>82915000</v>
+      </c>
+      <c r="E72" s="3">
         <v>88416000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>86448000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>84543000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>82380000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>78545000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>76401000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>73891000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>71993000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>70062000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>66310000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>63107000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>60464000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>58473000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>56746000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>54557000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>53147000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>50595000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>47945000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>46493000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>43542000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>44091000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>41657000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>39974000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>35635000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19373000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>18159000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>16153000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>15059000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12918000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6193,8 +6369,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6285,8 +6464,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6377,100 +6559,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>92430000</v>
+      </c>
+      <c r="E76" s="3">
         <v>97741000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>95193000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>92883000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>91144000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>87468000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>86016000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>83762000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>81790000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>77044000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>73684000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>71232000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>67842000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>65069000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>62697000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>60210000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>61395000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>58921000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>56582000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>55856000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>53145000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>54495000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>52024000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>50781000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>43096000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>26848000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>25189000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>23493000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>22524000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20460000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6561,197 +6749,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2705000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4762000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4648000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4909000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6577000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4900000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5199000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4580000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4613000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6407000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5800000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5245000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4588000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4357000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4700000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4156000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5095000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5194000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3944000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5032000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1939000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4924000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4120000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4545000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>18669000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3620000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4362000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3450000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4495000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6784,100 +6981,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4516000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4431000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4359000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4318000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4218000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4324000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4321000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4236000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4051000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3961000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4020000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4174000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4197000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4192000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4181000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4150000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4105000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4114000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4232000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4231000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4352000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4377000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4350000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4324000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4456000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4272000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4167000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4059000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3987000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6968,8 +7169,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7060,8 +7264,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7152,8 +7359,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7244,8 +7454,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7336,100 +7549,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8677000</v>
+      </c>
+      <c r="E89" s="3">
         <v>10778000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9731000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8289000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8942000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10534000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10844000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6821000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8377000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10724000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10744000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9694000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9296000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8920000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>14728000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>8824000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8998000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>10912000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8755000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>7081000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8095000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9811000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9785000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6648000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8084000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7303000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8237000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1681000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>5086000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4816000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7462,100 +7681,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8540000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4868000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4599000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6556000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8039000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5935000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5107000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7659000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6994000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6894000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4222000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4494000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4024000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4318000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4576000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5274000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5607000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4365000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3699000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4268000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4632000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4188000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3286000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4552000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5965000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4271000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3944000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6526000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-11570000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8506000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7646,8 +7869,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7738,100 +7964,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7824000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5408000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4090000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6110000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5342000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8664000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6661000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7995000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10135000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2617000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4748000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-49653000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5043000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6345000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5144000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6980000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5424000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3568000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3786000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4803000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4798000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4408000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3443000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5285000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5469000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3728000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4709000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4550000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8444000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5192000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7864,100 +8096,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-2794000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-2744000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2743000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2744000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-2739000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-2688000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-2724000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2654000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2648000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2599000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2597000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2601000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2596000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2546000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2543000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2547000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2542000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2493000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2492000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-2489000</v>
       </c>
       <c r="W96" s="3">
         <v>-2489000</v>
       </c>
       <c r="X96" s="3">
-        <v>-2438000</v>
+        <v>-2489000</v>
       </c>
       <c r="Y96" s="3">
         <v>-2438000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-2438000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-2407000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-2405000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-2357000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-2356000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-2354000</v>
       </c>
       <c r="AE96" s="3">
         <v>-2354000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-2354000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-2303000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8048,8 +8284,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8140,8 +8379,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8232,100 +8474,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3016000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6055000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3203000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2383000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3076000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1616000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4082000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>245000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5192000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3081000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11406000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>27956000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>9062000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1505000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-8795000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2563000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3863000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6258000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5386000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2657000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2956000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4556000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6549000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3497000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2765000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>4665000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-203000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>3977000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8416,96 +8664,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2163000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-685000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2438000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-204000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>524000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>254000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>101000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-929000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6950000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5026000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5410000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12003000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>13315000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1070000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>789000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4407000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-289000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1086000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-417000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-379000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>341000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>847000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-207000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>47000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2180000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-56000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>456000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1491000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3584000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>VZ</t>
   </si>
@@ -656,407 +656,419 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>32981000</v>
+      </c>
+      <c r="E8" s="3">
         <v>35130000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33336000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>32596000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32912000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>35251000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>34241000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33789000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33554000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>34067000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32915000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33764000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32867000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34692000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>31543000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>30447000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>31610000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34775000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>32894000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>32071000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>32128000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>34281000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>32607000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>32203000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>31772000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>33955000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>31717000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>30548000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>29814000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>32340000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>30937000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12872000</v>
+      </c>
+      <c r="E9" s="3">
         <v>15174000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13377000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12750000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13504000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15762000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14601000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14420000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14350000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14996000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13528000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14255000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13522000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14822000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12334000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>11749000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12296000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15631000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13384000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12721000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12990000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15291000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13331000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13328000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13255000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15387000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>20614000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12484000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12047000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>14362000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>12229000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>20109000</v>
+      </c>
+      <c r="E10" s="3">
         <v>19956000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>19959000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19846000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19408000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19489000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19640000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19369000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19204000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19071000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19387000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19509000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19345000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19870000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19209000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>18698000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19314000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19144000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19510000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19350000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19138000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>18990000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19276000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>18875000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>18517000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>18568000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>11103000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>18064000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>17767000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>17978000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>18708000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1090,8 +1102,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1185,8 +1198,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,198 +1296,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-110000</v>
+      </c>
+      <c r="E14" s="3">
         <v>7470000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>270000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>323000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-70000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-2214000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>645000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>198000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1241000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1230000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>948000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-168000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>223000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>404000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1092000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>255000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1377000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2381000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>291000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1544000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-96000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>4945000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>159000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>910000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>356000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2558000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>620000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-1015000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>722000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-1589000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>797000</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4445000</v>
+      </c>
+      <c r="E15" s="3">
         <v>4516000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4410000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4359000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4318000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4218000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4324000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4321000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4236000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4051000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3961000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4020000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4174000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4197000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4192000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4181000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4150000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4105000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4114000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4232000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4231000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4350000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4370000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4338000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4322000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4237000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>8544000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>12388000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>8118000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>3987000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1502,198 +1527,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25350000</v>
+      </c>
+      <c r="E17" s="3">
         <v>35438000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25778000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25307000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25258000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25508000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>26992000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>26435000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26999000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27689000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24958000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25431000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25097000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27695000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24957000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23341000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>25213000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>30127000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25005000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25765000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>24323000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>31991000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>24954000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>25586000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24672000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>30058000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>25183000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>22534000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>23700000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>24317000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>24397000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7631000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-308000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7558000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7289000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7654000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9743000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7249000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7354000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6555000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6378000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7957000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8333000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7770000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6997000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6586000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7106000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6397000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4648000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7889000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6306000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7805000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2290000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>7653000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6617000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7100000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3897000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>6534000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>8014000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>6114000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>8023000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6540000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1727,483 +1759,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E20" s="3">
         <v>90000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>67000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>108000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>53000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>173000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>208000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>288000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>314000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>505000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1218000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>335000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>409000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>336000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>309000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>197000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>313000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>223000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>180000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>219000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>193000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>276000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>233000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>132000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>155000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>256000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>141000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>171000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>200000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>63000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12155000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4298000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12056000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11756000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12025000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>14134000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11781000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11963000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11105000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10934000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13136000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12688000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12353000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11530000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11087000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11484000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>10860000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8976000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12183000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>10757000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>12229000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6918000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>12263000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11099000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11579000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>8609000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>10947000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>12352000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>10373000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>12073000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>10556000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1635000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1599000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1433000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1285000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1207000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1105000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>937000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>785000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>786000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>739000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>801000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>844000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1101000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1080000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1044000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1116000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1034000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1159000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1146000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1215000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1210000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1199000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1211000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1222000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1201000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1219000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1164000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1218000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1132000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1137000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1038000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6075000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1817000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6192000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6112000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6500000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8811000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6520000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6857000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6083000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6144000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8374000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7824000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7078000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6253000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5851000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6187000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5676000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3712000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6923000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5310000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6788000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1367000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6675000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5527000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6054000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2934000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5511000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6967000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5182000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>6949000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5576000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1353000</v>
+      </c>
+      <c r="E24" s="3">
         <v>756000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1308000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1346000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1482000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2113000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1496000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1542000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1372000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1407000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1820000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1875000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1700000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1535000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1347000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1348000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1389000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1505000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1586000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1236000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1628000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-698000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1613000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1281000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1388000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>912000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1775000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2489000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1629000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2349000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1829000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2297,198 +2345,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4722000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2573000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4884000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4766000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5018000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6698000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5024000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5315000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4711000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4737000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6554000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5949000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5378000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4718000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4504000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4839000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4287000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5217000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5337000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4074000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5160000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2065000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5062000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4246000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4666000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2022000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3736000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4478000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3553000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4600000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3747000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4602000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2705000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4762000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4648000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4909000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6577000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4900000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5199000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4580000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4613000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6407000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5800000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5245000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4588000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4357000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4700000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4156000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5095000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5194000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3944000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5032000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1939000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4924000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4120000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4545000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1908000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3620000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4362000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3450000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4495000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2582,8 +2639,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2641,17 +2701,17 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
+      <c r="X29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2659,11 +2719,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>16761000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2677,8 +2737,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2772,8 +2835,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2867,198 +2933,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-90000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-67000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-108000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-53000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-173000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-208000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-288000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-314000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-505000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1218000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-335000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-409000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-336000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-309000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-197000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-313000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-223000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-180000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-219000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-193000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-276000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-233000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-132000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-256000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-171000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-200000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-63000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-74000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4602000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2705000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4762000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4648000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4909000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6577000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4900000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5199000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4580000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4613000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6407000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5800000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5245000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4588000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4357000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4700000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4156000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5095000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5194000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3944000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5032000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1939000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4924000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4120000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4545000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>18669000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3620000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4362000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3450000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4495000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3152,203 +3227,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4602000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2705000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4762000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4648000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4909000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6577000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4900000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5199000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4580000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4613000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6407000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5800000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5245000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4588000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4357000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4700000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4156000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5095000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5194000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3944000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5032000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1939000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4924000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4120000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4545000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>18669000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3620000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4362000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3450000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4495000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3382,8 +3466,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3417,103 +3502,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2365000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2065000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4210000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4803000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2234000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2605000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2082000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1857000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1661000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2921000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9936000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4657000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10205000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>22171000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8983000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7882000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7047000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2594000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3020000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1949000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2322000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2745000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2538000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1750000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1923000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2079000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4487000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4583000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4307000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2880000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6441000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3607,673 +3696,697 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25860000</v>
+      </c>
+      <c r="E43" s="3">
         <v>25631000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>23851000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>23728000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>23436000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24506000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24362000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24606000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24335000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24585000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>22896000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>22029000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>23236000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24650000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>23350000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>23434000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>24641000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>26277000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>25531000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>25738000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>25239000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>25859000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>24765000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>23875000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>22595000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>23493000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>21549000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>19771000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>16863000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>17513000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>14832000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2076000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2057000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2240000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1896000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2381000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2388000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3133000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3646000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3659000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3055000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2303000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1421000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1303000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1796000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1457000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1289000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1633000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1422000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1538000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1167000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1417000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1336000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1270000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1102000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1285000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1276000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1116000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1194000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1202000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1318000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7656000</v>
+      </c>
+      <c r="E45" s="3">
         <v>7061000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7818000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6961000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7671000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8358000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10169000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7390000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5925000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6167000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5142000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7519000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4903000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5977000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4782000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4728000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7384000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7180000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4806000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4454000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4419000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4696000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4581000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4149000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5222000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3307000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3555000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3353000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4794000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4800000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3030000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>37957000</v>
+      </c>
+      <c r="E46" s="3">
         <v>36814000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>38119000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>37388000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35722000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37857000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>39746000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37499000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>35580000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36728000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>40277000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35626000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>39647000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>54594000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>38572000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>37333000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>40705000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>37473000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>34895000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>33308000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>33397000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>34636000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>33154000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>30876000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>31025000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>29913000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>30867000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>28823000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>27158000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>26395000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>25621000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1227000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1221000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1178000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1247000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1249000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1278000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1260000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1296000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1263000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1256000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1277000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>760000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>749000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>793000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>725000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>760000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>834000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>860000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>912000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>897000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>925000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>917000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>976000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1070000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>994000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1039000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1054000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1075000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1080000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1110000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1119000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>132214000</v>
+      </c>
+      <c r="E48" s="3">
         <v>133036000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>132576000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>132615000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>132934000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>133564000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>129592000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>128408000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>127337000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>127579000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>123725000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>122382000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>117191000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>117364000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>115862000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>115185000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>114649000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>114609000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>111067000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>110285000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>110954000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>89286000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>87464000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>87781000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>87922000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>88568000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>86622000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>86521000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>85213000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>84751000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>83414000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>189788000</v>
+      </c>
+      <c r="E49" s="3">
         <v>189567000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>195059000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>191081000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>190405000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>189928000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>189036000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>188648000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>188144000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>187899000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>177676000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>129951000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>132153000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>130283000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>130356000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>130034000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>126224000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>128946000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>128267000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>128439000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>128480000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>128519000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>132937000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>132916000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>132812000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>127836000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>127601000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>127674000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>124296000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>122775000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>121069000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4367,8 +4480,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4462,103 +4578,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18972000</v>
+      </c>
+      <c r="E52" s="3">
         <v>19617000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>17898000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17624000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17406000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>17053000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15456000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14296000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13392000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13134000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10502000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>60471000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>55833000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13447000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11479000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9947000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12088000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9839000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9734000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10179000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10191000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11471000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11031000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10660000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11763000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9787000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8538000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8885000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8984000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9149000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8275000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4652,103 +4774,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>380158000</v>
+      </c>
+      <c r="E54" s="3">
         <v>380255000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>384830000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>379955000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>377716000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>379680000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>375090000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>370147000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>365716000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>366596000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>353457000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>349190000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>345573000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>316481000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>296994000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>293259000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>294500000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>291727000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>284875000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>283108000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>283947000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>264829000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>265562000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>263303000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>264516000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>257143000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>254682000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>252978000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>246731000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>244180000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>239498000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4782,8 +4910,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4817,578 +4946,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20139000</v>
+      </c>
+      <c r="E57" s="3">
         <v>23453000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>26140000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20067000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19273000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23977000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22235000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>20956000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18169000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24833000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>20153000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17328000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17219000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>20658000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17391000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>19297000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17419000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>21806000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>19566000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>17633000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>18664000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>22501000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>19342000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>18560000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>17052000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>21232000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>18434000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>17825000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>14826000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>13876000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>18002000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15594000</v>
+      </c>
+      <c r="E58" s="3">
         <v>12973000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12950000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>14827000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12081000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9963000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>14995000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12873000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13421000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7443000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7623000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7023000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8802000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5889000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5770000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6651000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>11175000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>10777000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7830000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>8773000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>8614000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7190000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6502000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5466000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6323000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3453000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2180000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1153000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3707000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2645000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3852000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17898000</v>
+      </c>
+      <c r="E59" s="3">
         <v>16797000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16587000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16510000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16414000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16231000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15911000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15395000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14995000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14884000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13582000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15727000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12709000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13113000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13024000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12938000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12463000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12285000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11813000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11808000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11329000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8239000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8323000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8303000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8240000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8352000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8316000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8780000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8131000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>13819000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8444000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53631000</v>
+      </c>
+      <c r="E60" s="3">
         <v>53223000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>55677000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>51404000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47768000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>50171000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>53141000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>49224000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>46585000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>47160000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>41358000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>40078000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>38730000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>39660000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>36185000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>38886000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>41057000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>44868000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>39209000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38214000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38607000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>37930000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>34167000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>32329000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>31615000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>33037000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>28930000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>27758000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>26664000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>30340000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>30298000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>136104000</v>
+      </c>
+      <c r="E61" s="3">
         <v>137701000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>134441000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>137871000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>140772000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>140676000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>132912000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>136184000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>139961000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>143425000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>143352000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>144894000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>149700000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>123173000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>109790000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>106190000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>106561000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>100712000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>101769000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>104598000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>105045000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>105873000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>106440000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>109174000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>112734000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>113642000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>115317000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>116390000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>112839000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>105433000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>102739000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>94697000</v>
+      </c>
+      <c r="E62" s="3">
         <v>95532000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>95624000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>94178000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>94957000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>96370000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>100254000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>97382000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>93995000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>92811000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>90258000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>89106000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>84460000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>84376000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>84489000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>84070000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>85229000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>83312000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>83585000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>82349000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>82835000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>66316000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>68868000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>68225000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>67822000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>65777000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>81984000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>82069000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>82191000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>84375000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>84478000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5482,8 +5630,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5577,8 +5728,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5672,103 +5826,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>285824000</v>
+      </c>
+      <c r="E66" s="3">
         <v>287825000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>287089000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>284762000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>284833000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>288536000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>287622000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>284131000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>281954000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>284806000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>276413000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>275506000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>274341000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>248639000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>231925000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>230562000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>234290000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>230332000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>225954000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>226526000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>228091000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>211684000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>211067000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>211279000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>213735000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>214047000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>227834000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>227789000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>223238000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>221656000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>219038000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5802,8 +5962,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5897,8 +6058,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5992,8 +6156,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6087,8 +6254,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6182,103 +6352,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>84714000</v>
+      </c>
+      <c r="E72" s="3">
         <v>82915000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>88416000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>86448000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>84543000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>82380000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>78545000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>76401000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>73891000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>71993000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>70062000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>66310000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>63107000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>60464000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>58473000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>56746000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>54557000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>53147000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>50595000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>47945000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>46493000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>43542000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>44091000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>41657000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>39974000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>35635000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19373000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>18159000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>16153000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15059000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>12918000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6372,8 +6548,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6467,8 +6646,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6562,103 +6744,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>94334000</v>
+      </c>
+      <c r="E76" s="3">
         <v>92430000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>97741000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>95193000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>92883000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>91144000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>87468000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>86016000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>83762000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>81790000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>77044000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>73684000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>71232000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>67842000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>65069000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>62697000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>60210000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>61395000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>58921000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>56582000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>55856000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>53145000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>54495000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>52024000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>50781000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>43096000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>26848000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>25189000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>23493000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>22524000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20460000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6752,203 +6940,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4602000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2705000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4762000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4648000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4909000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6577000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4900000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5199000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4580000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4613000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6407000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5800000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5245000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4588000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4357000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4700000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4156000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5095000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5194000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3944000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5032000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1939000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4924000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4120000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4545000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>18669000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3620000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4362000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3450000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4495000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6982,103 +7179,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4445000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4516000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4431000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4359000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4318000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4218000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4324000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4321000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4236000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4051000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3961000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4020000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4174000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4197000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4192000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4181000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4150000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4105000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4114000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4232000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4231000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4352000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4377000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4350000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4324000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4456000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4272000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4167000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4059000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3987000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7172,8 +7373,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7267,8 +7471,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7362,8 +7569,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7457,8 +7667,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7552,103 +7765,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7084000</v>
+      </c>
+      <c r="E89" s="3">
         <v>8677000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10778000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9731000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8289000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8942000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10534000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10844000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6821000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8377000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10724000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10744000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9694000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9296000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8920000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>14728000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8824000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8998000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10912000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8755000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7081000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8095000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9811000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9785000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6648000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8084000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7303000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8237000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1681000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>5086000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4816000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7682,103 +7901,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4825000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8540000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4868000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4599000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6556000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8039000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5935000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5107000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7659000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6994000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6894000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4222000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4494000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4024000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4318000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4576000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5274000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5607000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4365000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3699000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4268000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4632000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4188000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3286000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4552000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5965000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4271000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3944000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-6526000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11570000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8506000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7872,8 +8095,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7967,103 +8193,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5245000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7824000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5408000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4090000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6110000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5342000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8664000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6661000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7995000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10135000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2617000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4748000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-49653000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5043000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6345000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5144000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6980000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5424000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3568000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3786000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4803000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4798000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4408000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3443000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5285000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5469000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3728000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4709000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4550000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-8444000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5192000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8097,103 +8329,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-2796000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-2794000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2744000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2743000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-2744000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-2739000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-2688000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2724000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2654000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2648000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2599000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2597000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2601000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2596000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2546000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2543000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2547000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2542000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2493000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2492000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-2489000</v>
       </c>
       <c r="X96" s="3">
         <v>-2489000</v>
       </c>
       <c r="Y96" s="3">
-        <v>-2438000</v>
+        <v>-2489000</v>
       </c>
       <c r="Z96" s="3">
         <v>-2438000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-2438000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-2407000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-2405000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-2357000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-2356000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-2354000</v>
       </c>
       <c r="AF96" s="3">
         <v>-2354000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-2354000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-2303000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8287,8 +8523,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8382,8 +8621,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8477,103 +8719,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1428000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3016000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6055000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3203000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2383000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3076000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1616000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4082000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>245000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5192000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3081000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11406000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>27956000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>9062000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1505000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8795000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2563000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3863000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6258000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-5386000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2657000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2956000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4556000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6549000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3497000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2765000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>4665000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-203000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>3977000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8667,99 +8915,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>411000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2163000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-685000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2438000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-204000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>524000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>254000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>101000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-929000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6950000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5026000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5410000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12003000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>13315000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1070000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>789000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4407000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-289000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1086000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-417000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-379000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>341000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>847000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-207000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>47000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2180000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-56000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>456000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1491000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3584000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>VZ</t>
   </si>
@@ -656,419 +656,431 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>32796000</v>
+      </c>
+      <c r="E8" s="3">
         <v>32981000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35130000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>33336000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32596000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>32912000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>35251000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>34241000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33789000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33554000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>34067000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>32915000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33764000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>32867000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34692000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>31543000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>30447000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>31610000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>34775000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>32894000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>32071000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>32128000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>34281000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>32607000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>32203000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>31772000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>33955000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>31717000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>30548000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>29814000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>32340000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>30937000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12471000</v>
+      </c>
+      <c r="E9" s="3">
         <v>12872000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15174000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13377000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12750000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13504000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15762000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14601000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14420000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14350000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14996000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13528000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14255000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13522000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14822000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12334000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>11749000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12296000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15631000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13384000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12721000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12990000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>15291000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13331000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13328000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13255000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>15387000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>20614000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12484000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>12047000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>14362000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>12229000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>20325000</v>
+      </c>
+      <c r="E10" s="3">
         <v>20109000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>19956000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19959000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19846000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19408000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19489000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19640000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19369000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19204000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19071000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19387000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19509000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19345000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19870000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>19209000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>18698000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19314000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19144000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19510000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19350000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19138000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>18990000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>19276000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>18875000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>18517000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>18568000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>11103000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>18064000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>17767000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>17978000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>18708000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1103,8 +1115,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1201,8 +1214,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,204 +1315,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-110000</v>
+        <v>266000</v>
       </c>
       <c r="E14" s="3">
+        <v>217000</v>
+      </c>
+      <c r="F14" s="3">
         <v>7470000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>270000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>323000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-70000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2214000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>645000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>198000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1241000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1230000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>948000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-168000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>223000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>404000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1092000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>255000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1377000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2381000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>291000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1544000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-96000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>4945000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>159000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>910000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>356000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2558000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>620000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-1015000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>722000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-1589000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>797000</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>4445000</v>
+        <v>4264000</v>
       </c>
       <c r="E15" s="3">
+        <v>4224000</v>
+      </c>
+      <c r="F15" s="3">
         <v>4516000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4410000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4359000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4318000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4218000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4324000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4321000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4236000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4051000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3961000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4020000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4174000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4197000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4192000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4181000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4150000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4105000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4114000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4232000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4231000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4350000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4370000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4338000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4322000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4237000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>8544000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>12388000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>8118000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>3987000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1528,204 +1553,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25025000</v>
+      </c>
+      <c r="E17" s="3">
         <v>25350000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35438000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25778000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25307000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25258000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25508000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>26992000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26435000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26999000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27689000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24958000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25431000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25097000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27695000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>24957000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23341000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25213000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>30127000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25005000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>25765000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>24323000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>31991000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>24954000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>25586000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>24672000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>30058000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>25183000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>22534000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>23700000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>24317000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>24397000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7771000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7631000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-308000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7558000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7289000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7654000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9743000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7249000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7354000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6555000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6378000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7957000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8333000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7770000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6997000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6586000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7106000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6397000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4648000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7889000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6306000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7805000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2290000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7653000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6617000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>7100000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3897000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>6534000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>8014000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6114000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>8023000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>6540000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1760,498 +1792,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E20" s="3">
         <v>79000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>90000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>67000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>108000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>53000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>173000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>208000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>288000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>314000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>505000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1218000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>335000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>409000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>336000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>309000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>197000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>313000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>223000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>180000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>219000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>193000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>276000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>233000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>132000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>155000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>256000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>141000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>171000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>200000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>63000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12215000</v>
+      </c>
+      <c r="E21" s="3">
         <v>12155000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4298000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12056000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11756000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12025000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>14134000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11781000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11963000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11105000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10934000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13136000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12688000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12353000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11530000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11087000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11484000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10860000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>8976000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12183000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>10757000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>12229000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6918000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>12263000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11099000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>11579000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>8609000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>10947000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>12352000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>10373000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>12073000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>10556000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1698000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1635000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1599000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1433000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1285000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1207000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1105000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>937000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>785000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>786000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>739000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>801000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>844000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1101000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1080000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1044000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1116000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1034000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1159000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1146000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1215000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1210000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1199000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1211000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1222000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1201000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1219000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1164000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1218000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1132000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1137000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1038000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6034000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6075000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1817000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6192000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6112000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6500000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8811000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6520000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6857000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6083000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6144000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8374000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7824000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7078000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6253000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5851000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6187000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5676000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3712000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6923000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5310000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6788000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1367000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6675000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5527000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6054000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2934000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5511000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6967000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5182000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>6949000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5576000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1353000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>756000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1308000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1346000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1482000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2113000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1496000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1542000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1372000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1407000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1820000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1875000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1700000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1535000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1347000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1348000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1389000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1505000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1586000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1236000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1628000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-698000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1613000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1281000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1388000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>912000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1775000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2489000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1629000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2349000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1829000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2348,204 +2396,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4702000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4722000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2573000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4884000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4766000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5018000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6698000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5024000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5315000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4711000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4737000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6554000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5949000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5378000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4718000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4504000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4839000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4287000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5217000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5337000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4074000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5160000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2065000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5062000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4246000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4666000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2022000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3736000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4478000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3553000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4600000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3747000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4593000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4602000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2705000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4762000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4648000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4909000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6577000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4900000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5199000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4580000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4613000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6407000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5800000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5245000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4588000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4357000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4700000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4156000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5095000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5194000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3944000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5032000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1939000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4924000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4120000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4545000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1908000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3620000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4362000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3450000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4495000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2642,8 +2699,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2704,17 +2764,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2722,11 +2782,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>16761000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2740,8 +2800,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2838,8 +2901,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2936,204 +3002,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-79000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-90000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-67000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-108000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-53000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-173000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-208000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-288000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-314000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-505000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1218000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-335000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-409000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-336000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-309000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-197000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-313000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-223000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-180000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-219000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-193000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-276000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-233000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-132000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-256000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-171000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-200000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-63000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-74000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4593000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4602000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2705000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4762000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4648000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4909000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6577000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4900000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5199000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4580000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4613000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6407000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5800000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5245000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4588000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4357000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4700000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4156000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5095000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5194000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3944000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5032000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1939000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4924000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4120000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4545000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>18669000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3620000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4362000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3450000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4495000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3230,209 +3305,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4593000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4602000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2705000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4762000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4648000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4909000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6577000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4900000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5199000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4580000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4613000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6407000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5800000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5245000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4588000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4357000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4700000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4156000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5095000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5194000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3944000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5032000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1939000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4924000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4120000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4545000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>18669000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3620000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4362000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3450000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4495000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3467,8 +3551,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3503,106 +3588,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2432000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2365000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2065000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4210000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4803000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2234000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2605000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2082000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1857000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1661000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2921000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9936000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4657000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10205000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>22171000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8983000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7882000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7047000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2594000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3020000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1949000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2322000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2745000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2538000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1750000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1923000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2079000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4487000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4583000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4307000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2880000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6441000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3699,694 +3788,718 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26155000</v>
+      </c>
+      <c r="E43" s="3">
         <v>25860000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25631000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>23851000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>23728000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>23436000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24506000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24362000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24606000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24335000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24585000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>22896000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>22029000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>23236000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24650000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>23350000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>23434000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>24641000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>26277000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>25531000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>25738000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>25239000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>25859000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>24765000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>23875000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>22595000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>23493000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>21549000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>19771000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>16863000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>17513000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>14832000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1841000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2076000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2057000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2240000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1896000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2381000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2388000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3133000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3646000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3659000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3055000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2303000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1421000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1303000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1796000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1457000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1289000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1633000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1422000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1538000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1167000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1417000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1336000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1270000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1102000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1285000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1276000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1116000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1194000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1202000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1318000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7628000</v>
+      </c>
+      <c r="E45" s="3">
         <v>7656000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7061000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7818000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6961000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7671000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8358000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10169000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7390000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5925000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6167000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5142000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7519000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4903000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5977000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4782000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4728000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7384000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7180000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4806000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4454000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4419000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4696000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4581000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4149000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5222000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3307000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3555000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3353000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4794000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4800000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3030000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>38056000</v>
+      </c>
+      <c r="E46" s="3">
         <v>37957000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>36814000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38119000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>37388000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>35722000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37857000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>39746000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>37499000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>35580000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>36728000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>40277000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>35626000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>39647000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>54594000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>38572000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>37333000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>40705000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>37473000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>34895000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>33308000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>33397000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>34636000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>33154000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>30876000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>31025000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>29913000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>30867000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>28823000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>27158000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>26395000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>25621000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1195000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1227000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1221000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1178000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1247000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1249000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1278000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1260000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1296000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1263000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1256000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1277000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>760000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>749000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>793000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>725000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>760000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>834000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>860000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>912000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>897000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>925000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>917000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>976000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1070000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>994000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1039000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1054000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1075000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1080000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1110000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1119000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>131954000</v>
+      </c>
+      <c r="E48" s="3">
         <v>132214000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>133036000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>132576000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>132615000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>132934000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>133564000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>129592000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>128408000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>127337000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>127579000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>123725000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>122382000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>117191000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>117364000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>115862000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>115185000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>114649000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>114609000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>111067000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>110285000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>110954000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>89286000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>87464000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>87781000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>87922000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>88568000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>86622000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>86521000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>85213000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>84751000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>83414000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>189813000</v>
+      </c>
+      <c r="E49" s="3">
         <v>189788000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>189567000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>195059000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>191081000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>190405000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>189928000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>189036000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>188648000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>188144000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>187899000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>177676000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>129951000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>132153000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>130283000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>130356000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>130034000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>126224000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>128946000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>128267000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>128439000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>128480000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>128519000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>132937000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>132916000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>132812000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>127836000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>127601000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>127674000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>124296000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>122775000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>121069000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4483,8 +4596,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4581,106 +4697,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18128000</v>
+      </c>
+      <c r="E52" s="3">
         <v>18972000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19617000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17898000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17624000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>17406000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17053000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15456000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14296000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13392000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13134000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10502000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>60471000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>55833000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13447000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11479000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9947000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12088000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9839000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9734000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10179000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10191000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11471000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11031000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10660000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11763000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9787000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8538000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8885000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8984000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9149000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8275000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4777,106 +4899,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>379146000</v>
+      </c>
+      <c r="E54" s="3">
         <v>380158000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>380255000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>384830000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>379955000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>377716000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>379680000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>375090000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>370147000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>365716000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>366596000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>353457000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>349190000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>345573000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>316481000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>296994000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>293259000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>294500000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>291727000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>284875000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>283108000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>283947000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>264829000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>265562000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>263303000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>264516000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>257143000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>254682000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>252978000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>246731000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>244180000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>239498000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4911,8 +5039,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4947,596 +5076,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19727000</v>
+      </c>
+      <c r="E57" s="3">
         <v>20139000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>23453000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>26140000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20067000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>19273000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23977000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22235000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>20956000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18169000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24833000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>20153000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17328000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17219000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>20658000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17391000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19297000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>17419000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>21806000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>19566000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>17633000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>18664000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>22501000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>19342000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>18560000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>17052000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>21232000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>18434000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>17825000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>14826000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>13876000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>18002000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>23255000</v>
+      </c>
+      <c r="E58" s="3">
         <v>15594000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12973000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12950000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>14827000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12081000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9963000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14995000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12873000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13421000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7443000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7623000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7023000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8802000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5889000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5770000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6651000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>11175000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>10777000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7830000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>8773000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>8614000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7190000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6502000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5466000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6323000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3453000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2180000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1153000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3707000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2645000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3852000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17824000</v>
+      </c>
+      <c r="E59" s="3">
         <v>17898000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16797000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16587000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16510000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16414000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16231000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15911000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15395000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14995000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14884000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13582000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15727000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12709000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13113000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13024000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12938000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12463000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12285000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11813000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11808000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11329000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8239000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8323000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8303000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8240000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8352000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8316000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8780000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8131000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>13819000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8444000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>60806000</v>
+      </c>
+      <c r="E60" s="3">
         <v>53631000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53223000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>55677000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>51404000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>47768000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>50171000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>53141000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>49224000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>46585000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>47160000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>41358000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>40078000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>38730000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>39660000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>36185000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>38886000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>41057000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>44868000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>39209000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38214000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>38607000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>37930000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>34167000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>32329000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>31615000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>33037000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>28930000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>27758000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>26664000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>30340000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>30298000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>126022000</v>
+      </c>
+      <c r="E61" s="3">
         <v>136104000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>137701000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>134441000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>137871000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>140772000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>140676000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>132912000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>136184000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>139961000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>143425000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>143352000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>144894000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>149700000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>123173000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>109790000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>106190000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>106561000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>100712000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>101769000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>104598000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>105045000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>105873000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>106440000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>109174000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>112734000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>113642000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>115317000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>116390000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>112839000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>105433000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>102739000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>94779000</v>
+      </c>
+      <c r="E62" s="3">
         <v>94697000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>95532000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>95624000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>94178000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>94957000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>96370000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>100254000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>97382000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>93995000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>92811000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>90258000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>89106000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>84460000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>84376000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>84489000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>84070000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>85229000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>83312000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>83585000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>82349000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>82835000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>66316000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>68868000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>68225000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>67822000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>65777000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>81984000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>82069000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>82191000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>84375000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>84478000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5633,8 +5781,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5731,8 +5882,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5829,106 +5983,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>282974000</v>
+      </c>
+      <c r="E66" s="3">
         <v>285824000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>287825000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>287089000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>284762000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>284833000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>288536000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>287622000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>284131000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>281954000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>284806000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>276413000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>275506000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>274341000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>248639000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>231925000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>230562000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>234290000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>230332000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>225954000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>226526000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>228091000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>211684000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>211067000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>211279000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>213735000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>214047000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>227834000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>227789000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>223238000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>221656000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>219038000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5963,8 +6123,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6061,8 +6222,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6159,8 +6323,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6257,8 +6424,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6355,106 +6525,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>86504000</v>
+      </c>
+      <c r="E72" s="3">
         <v>84714000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>82915000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>88416000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>86448000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>84543000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>82380000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>78545000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>76401000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>73891000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>71993000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>70062000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>66310000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>63107000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>60464000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>58473000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>56746000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>54557000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>53147000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>50595000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>47945000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>46493000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>43542000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>44091000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>41657000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>39974000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>35635000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19373000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>18159000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>16153000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>15059000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>12918000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6551,8 +6727,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6649,8 +6828,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6747,106 +6929,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>96172000</v>
+      </c>
+      <c r="E76" s="3">
         <v>94334000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>92430000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>97741000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>95193000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>92883000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>91144000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>87468000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>86016000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>83762000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>81790000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>77044000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>73684000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>71232000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>67842000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>65069000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>62697000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>60210000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>61395000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>58921000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>56582000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>55856000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>53145000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>54495000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>52024000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>50781000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>43096000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>26848000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>25189000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>23493000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>22524000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20460000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6943,209 +7131,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4593000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4602000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2705000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4762000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4648000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4909000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6577000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4900000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5199000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4580000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4613000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6407000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5800000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5245000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4588000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4357000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4700000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4156000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5095000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5194000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3944000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5032000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1939000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4924000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4120000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4545000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>18669000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3620000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4362000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3450000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4495000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7180,106 +7377,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4483000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4445000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4516000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4431000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4359000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4318000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4218000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4324000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4321000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4236000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4051000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3961000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4020000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4174000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4197000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4192000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4181000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4150000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4105000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4114000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4232000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4231000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4352000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4377000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4350000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4324000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4456000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4272000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4167000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4059000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3987000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7376,8 +7577,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7474,8 +7678,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7572,8 +7779,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7670,8 +7880,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7768,106 +7981,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9485000</v>
+      </c>
+      <c r="E89" s="3">
         <v>7084000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8677000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10778000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9731000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8289000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8942000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10534000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10844000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6821000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8377000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10724000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10744000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9694000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9296000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>8920000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>14728000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8824000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8998000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>10912000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8755000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7081000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8095000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9811000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>9785000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6648000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8084000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7303000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>8237000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1681000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>5086000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4816000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7902,106 +8121,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3859000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4825000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8540000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4868000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4599000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6556000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8039000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5935000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5107000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7659000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6994000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6894000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4222000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4494000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4024000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4318000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4576000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5274000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5607000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4365000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3699000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4268000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4632000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4188000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3286000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4552000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5965000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4271000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3944000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-6526000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-11570000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8506000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8098,8 +8321,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8196,106 +8422,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3865000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5245000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7824000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5408000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4090000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6110000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5342000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8664000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6661000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7995000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10135000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2617000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4748000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-49653000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5043000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6345000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5144000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6980000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5424000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3568000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3786000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4803000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4798000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4408000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3443000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5285000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5469000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3728000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4709000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4550000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-8444000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-5192000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8330,106 +8562,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-2802000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-2796000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2794000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2744000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-2743000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-2744000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-2739000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2688000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2724000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2654000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2648000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2599000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2597000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2601000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2596000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2546000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2543000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2547000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2542000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2493000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2492000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-2489000</v>
       </c>
       <c r="Y96" s="3">
         <v>-2489000</v>
       </c>
       <c r="Z96" s="3">
-        <v>-2438000</v>
+        <v>-2489000</v>
       </c>
       <c r="AA96" s="3">
         <v>-2438000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-2438000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-2407000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-2405000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-2357000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-2356000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-2354000</v>
       </c>
       <c r="AG96" s="3">
         <v>-2354000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-2354000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-2303000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8526,8 +8762,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8624,8 +8863,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8722,106 +8964,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5634000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1428000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3016000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6055000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3203000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2383000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3076000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1616000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4082000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>245000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5192000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3081000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-11406000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>27956000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>9062000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1505000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8795000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2563000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3863000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6258000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5386000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2657000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2956000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4556000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-6549000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3497000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2765000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>4665000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-203000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>3977000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8918,102 +9166,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E102" s="3">
         <v>411000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2163000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-685000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2438000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-204000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>524000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>254000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>101000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-929000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6950000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5026000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5410000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12003000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>13315000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1070000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>789000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4407000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-289000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1086000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-417000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-379000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>341000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>847000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-207000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>47000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2180000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-56000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>456000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1491000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>3584000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>VZ</t>
   </si>
@@ -656,431 +656,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>33330000</v>
+      </c>
+      <c r="E8" s="3">
         <v>32796000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>32981000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35130000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>33336000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>32596000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32912000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>35251000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>34241000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33789000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33554000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34067000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32915000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33764000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>32867000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34692000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>31543000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>30447000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>31610000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>34775000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>32894000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>32071000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>32128000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>34281000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>32607000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>32203000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>31772000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>33955000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>31717000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>30548000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>29814000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>32340000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>30937000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13051000</v>
+      </c>
+      <c r="E9" s="3">
         <v>12471000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12872000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15174000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13377000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12750000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13504000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15762000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14601000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14420000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14350000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14996000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13528000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14255000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13522000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14822000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12334000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>11749000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12296000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15631000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13384000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12721000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12990000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>15291000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13331000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13328000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13255000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>15387000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>20614000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>12484000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>12047000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>14362000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>12229000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>20279000</v>
+      </c>
+      <c r="E10" s="3">
         <v>20325000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20109000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19956000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19959000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19846000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19408000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19489000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19640000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19369000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19204000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19071000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19387000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19509000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19345000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>19870000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19209000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>18698000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19314000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19144000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19510000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19350000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19138000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>18990000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>19276000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>18875000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>18517000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>18568000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>11103000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>18064000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>17767000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>17978000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>18708000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1116,8 +1128,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1217,8 +1230,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1318,210 +1334,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>266000</v>
+        <v>2017000</v>
       </c>
       <c r="E14" s="3">
-        <v>217000</v>
+        <v>47000</v>
       </c>
       <c r="F14" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="G14" s="3">
         <v>7470000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>270000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>323000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-70000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2214000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>645000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>198000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1241000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1230000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>948000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-168000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>223000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>404000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1092000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>255000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1377000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2381000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>291000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1544000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-96000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>4945000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>159000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>910000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>356000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2558000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>620000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-1015000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>722000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-1589000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>797000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>4264000</v>
+        <v>4458000</v>
       </c>
       <c r="E15" s="3">
-        <v>4224000</v>
+        <v>4483000</v>
       </c>
       <c r="F15" s="3">
+        <v>4445000</v>
+      </c>
+      <c r="G15" s="3">
         <v>4516000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4410000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4359000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4318000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4218000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4324000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4321000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4236000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4051000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3961000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4020000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4174000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4197000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4192000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4181000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4150000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4105000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4114000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4232000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4231000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4350000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4370000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4338000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4322000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4237000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>8544000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>12388000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>8118000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>3987000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1554,210 +1579,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>25025000</v>
+        <v>25353000</v>
       </c>
       <c r="E17" s="3">
-        <v>25350000</v>
+        <v>25211000</v>
       </c>
       <c r="F17" s="3">
-        <v>35438000</v>
+        <v>25354000</v>
       </c>
       <c r="G17" s="3">
-        <v>25778000</v>
+        <v>27955000</v>
       </c>
       <c r="H17" s="3">
-        <v>25307000</v>
+        <v>25493000</v>
       </c>
       <c r="I17" s="3">
-        <v>25258000</v>
+        <v>24971000</v>
       </c>
       <c r="J17" s="3">
+        <v>25315000</v>
+      </c>
+      <c r="K17" s="3">
         <v>25508000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26992000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26435000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>26999000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27689000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24958000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25431000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25097000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>27695000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>24957000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23341000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25213000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>30127000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>25005000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>25765000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>24323000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>31991000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24954000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>25586000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>24672000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>30058000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>25183000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>22534000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>23700000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>24317000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>24397000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7771000</v>
+        <v>7977000</v>
       </c>
       <c r="E18" s="3">
-        <v>7631000</v>
+        <v>7585000</v>
       </c>
       <c r="F18" s="3">
-        <v>-308000</v>
+        <v>7627000</v>
       </c>
       <c r="G18" s="3">
-        <v>7558000</v>
+        <v>7175000</v>
       </c>
       <c r="H18" s="3">
-        <v>7289000</v>
+        <v>7843000</v>
       </c>
       <c r="I18" s="3">
-        <v>7654000</v>
+        <v>7625000</v>
       </c>
       <c r="J18" s="3">
+        <v>7597000</v>
+      </c>
+      <c r="K18" s="3">
         <v>9743000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7249000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7354000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6555000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6378000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7957000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8333000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7770000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6997000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6586000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7106000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6397000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4648000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7889000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6306000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>7805000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2290000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7653000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>6617000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>7100000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3897000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>6534000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>8014000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6114000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>8023000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>6540000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1793,513 +1825,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-39000</v>
+        <v>83000</v>
       </c>
       <c r="E20" s="3">
-        <v>79000</v>
+        <v>-111000</v>
       </c>
       <c r="F20" s="3">
-        <v>90000</v>
+        <v>-1000</v>
       </c>
       <c r="G20" s="3">
-        <v>67000</v>
+        <v>12000</v>
       </c>
       <c r="H20" s="3">
-        <v>108000</v>
+        <v>46000</v>
       </c>
       <c r="I20" s="3">
-        <v>53000</v>
+        <v>-3000</v>
       </c>
       <c r="J20" s="3">
+        <v>35000</v>
+      </c>
+      <c r="K20" s="3">
         <v>173000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>208000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>288000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>314000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>505000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1218000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>335000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>409000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>336000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>309000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>197000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>313000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>223000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>180000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>219000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>193000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>276000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>233000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>132000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>155000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>256000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>141000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>171000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>200000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>63000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>12215000</v>
+        <v>12352000</v>
       </c>
       <c r="E21" s="3">
-        <v>12155000</v>
+        <v>12179000</v>
       </c>
       <c r="F21" s="3">
-        <v>4298000</v>
+        <v>12073000</v>
       </c>
       <c r="G21" s="3">
-        <v>12056000</v>
+        <v>11679000</v>
       </c>
       <c r="H21" s="3">
-        <v>11756000</v>
+        <v>12207000</v>
       </c>
       <c r="I21" s="3">
-        <v>12025000</v>
+        <v>11987000</v>
       </c>
       <c r="J21" s="3">
+        <v>11880000</v>
+      </c>
+      <c r="K21" s="3">
         <v>14134000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11781000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11963000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11105000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10934000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13136000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12688000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12353000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11530000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11087000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11484000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>10860000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8976000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>12183000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>10757000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>12229000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6918000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>12263000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>11099000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>11579000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>8609000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>10947000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>12352000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>10373000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>12073000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>10556000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1672000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1698000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1635000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1599000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1433000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1285000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1207000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1105000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>937000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>785000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>786000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>739000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>801000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>844000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1101000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1080000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1044000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1116000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1034000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1159000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1146000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1215000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1210000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1199000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1211000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1222000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1201000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1219000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1164000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1218000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1132000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1137000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1038000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4302000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6034000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6075000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1817000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6192000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6112000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6500000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8811000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6520000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6857000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6083000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6144000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8374000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7824000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7078000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6253000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5851000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6187000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5676000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3712000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6923000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5310000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6788000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1367000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6675000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5527000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6054000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2934000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5511000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>6967000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5182000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>6949000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>5576000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>891000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1332000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1353000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>756000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1308000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1346000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1482000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2113000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1496000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1542000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1372000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1407000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1820000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1875000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1700000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1535000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1347000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1348000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1389000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1505000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1586000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1236000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1628000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-698000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1613000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1281000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1388000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>912000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1775000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2489000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1629000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2349000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1829000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,210 +2447,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3411000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4702000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4722000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2573000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4884000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4766000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5018000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6698000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5024000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5315000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4711000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4737000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6554000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5949000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5378000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4718000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4504000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4839000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4287000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5217000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5337000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4074000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5160000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2065000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5062000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4246000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4666000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2022000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3736000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4478000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3553000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4600000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3747000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3306000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4593000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4602000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2705000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4762000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4648000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4909000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6577000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4900000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5199000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4580000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4613000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6407000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5800000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5245000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4588000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4357000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4700000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4156000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5095000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5194000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3944000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5032000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1939000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4924000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4120000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4545000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1908000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3620000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4362000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3450000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4495000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2702,8 +2759,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2767,17 +2827,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
+      <c r="Z29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2785,11 +2845,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>16761000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2803,8 +2863,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2904,8 +2967,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3005,210 +3071,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>39000</v>
+        <v>-83000</v>
       </c>
       <c r="E32" s="3">
-        <v>-79000</v>
+        <v>111000</v>
       </c>
       <c r="F32" s="3">
-        <v>-90000</v>
+        <v>1000</v>
       </c>
       <c r="G32" s="3">
-        <v>-67000</v>
+        <v>-12000</v>
       </c>
       <c r="H32" s="3">
-        <v>-108000</v>
+        <v>-46000</v>
       </c>
       <c r="I32" s="3">
-        <v>-53000</v>
+        <v>3000</v>
       </c>
       <c r="J32" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-173000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-208000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-288000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-314000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-505000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1218000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-335000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-409000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-336000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-309000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-197000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-313000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-223000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-180000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-219000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-193000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-276000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-233000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-132000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-256000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-171000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-200000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-63000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-74000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3306000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4593000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4602000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2705000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4762000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4648000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4909000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6577000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4900000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5199000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4580000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4613000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6407000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5800000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5245000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4588000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4357000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4700000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4156000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5095000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5194000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3944000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5032000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1939000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4924000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4120000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4545000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>18669000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3620000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4362000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3450000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4495000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3308,215 +3383,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3306000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4593000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4602000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2705000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4762000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4648000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4909000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6577000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4900000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5199000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4580000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4613000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6407000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5800000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5245000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4588000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4357000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4700000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4156000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5095000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5194000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3944000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5032000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1939000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4924000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4120000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4545000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>18669000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3620000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4362000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3450000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4495000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3552,8 +3636,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3589,132 +3674,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4987000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2432000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2365000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2065000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4210000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4803000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2234000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2605000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2082000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1857000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1661000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2921000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9936000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4657000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10205000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22171000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8983000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7882000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7047000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2594000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3020000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1949000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2322000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2745000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2538000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1750000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1923000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2079000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4487000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4583000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4307000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2880000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6441000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>117000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>117000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3791,715 +3880,739 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26523000</v>
+      </c>
+      <c r="E43" s="3">
         <v>26155000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25860000</v>
       </c>
-      <c r="F43" s="3">
-        <v>25631000</v>
-      </c>
       <c r="G43" s="3">
-        <v>23851000</v>
+        <v>25085000</v>
       </c>
       <c r="H43" s="3">
+        <v>24143000</v>
+      </c>
+      <c r="I43" s="3">
         <v>23728000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>23436000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24506000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24362000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24606000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24335000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24585000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>22896000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>22029000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>23236000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24650000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>23350000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>23434000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>24641000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>26277000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>25531000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>25738000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>25239000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>25859000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>24765000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>23875000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>22595000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>23493000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>21549000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>19771000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>16863000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>17513000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>14832000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2523000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1841000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2076000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2057000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2240000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1896000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2381000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2388000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3133000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3646000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3659000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3055000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2303000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1421000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1303000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1796000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1457000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1289000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1633000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1422000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1538000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1167000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1417000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1336000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1270000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1102000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1285000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1276000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1116000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1194000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1202000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1318000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7628000</v>
+        <v>2846000</v>
       </c>
       <c r="E45" s="3">
-        <v>7656000</v>
+        <v>4613000</v>
       </c>
       <c r="F45" s="3">
-        <v>7061000</v>
+        <v>4581000</v>
       </c>
       <c r="G45" s="3">
-        <v>7818000</v>
+        <v>4162000</v>
       </c>
       <c r="H45" s="3">
-        <v>6961000</v>
+        <v>2675000</v>
       </c>
       <c r="I45" s="3">
-        <v>7671000</v>
+        <v>4134000</v>
       </c>
       <c r="J45" s="3">
+        <v>4578000</v>
+      </c>
+      <c r="K45" s="3">
         <v>8358000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10169000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7390000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5925000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6167000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5142000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7519000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4903000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5977000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4782000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4728000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7384000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7180000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4806000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4454000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4419000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4696000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4581000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4149000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5222000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3307000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3555000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3353000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4794000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4800000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3030000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>40641000</v>
+      </c>
+      <c r="E46" s="3">
         <v>38056000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>37957000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>36814000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>38119000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37388000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>35722000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37857000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>39746000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>37499000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>35580000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>36728000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>40277000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>35626000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>39647000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>54594000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>38572000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>37333000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>40705000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>37473000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>34895000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>33308000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>33397000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>34636000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>33154000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>30876000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>31025000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>29913000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>30867000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>28823000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>27158000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>26395000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>25621000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1195000</v>
+        <v>1142000</v>
       </c>
       <c r="E47" s="3">
-        <v>1227000</v>
+        <v>1179000</v>
       </c>
       <c r="F47" s="3">
-        <v>1221000</v>
+        <v>1211000</v>
       </c>
       <c r="G47" s="3">
-        <v>1178000</v>
+        <v>1214000</v>
       </c>
       <c r="H47" s="3">
-        <v>1247000</v>
+        <v>1176000</v>
       </c>
       <c r="I47" s="3">
-        <v>1249000</v>
+        <v>1305000</v>
       </c>
       <c r="J47" s="3">
+        <v>1360000</v>
+      </c>
+      <c r="K47" s="3">
         <v>1278000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1260000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1296000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1263000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1256000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1277000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>760000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>749000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>793000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>725000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>760000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>834000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>860000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>912000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>897000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>925000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>917000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>976000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1070000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>994000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1039000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1054000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1075000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1080000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1110000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1119000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>131141000</v>
+      </c>
+      <c r="E48" s="3">
         <v>131954000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>132214000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>133036000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>132576000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>132615000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>132934000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>133564000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>129592000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>128408000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>127337000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>127579000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>123725000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>122382000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>117191000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>117364000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>115862000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>115185000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>114649000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>114609000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>111067000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>110285000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>110954000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>89286000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>87464000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>87781000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>87922000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>88568000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>86622000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>86521000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>85213000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>84751000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>83414000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>189999000</v>
+      </c>
+      <c r="E49" s="3">
         <v>189813000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>189788000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>189567000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>195059000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>191081000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>190405000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>189928000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>189036000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>188648000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>188144000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>187899000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>177676000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>129951000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>132153000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>130283000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>130356000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>130034000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>126224000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>128946000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>128267000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>128439000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>128480000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>128519000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>132937000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>132916000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>132812000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>127836000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>127601000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>127674000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>124296000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>122775000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>121069000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4599,8 +4712,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4700,109 +4816,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>18128000</v>
+        <v>2622000</v>
       </c>
       <c r="E52" s="3">
-        <v>18972000</v>
+        <v>2324000</v>
       </c>
       <c r="F52" s="3">
-        <v>19617000</v>
+        <v>2483000</v>
       </c>
       <c r="G52" s="3">
-        <v>17898000</v>
+        <v>2593000</v>
       </c>
       <c r="H52" s="3">
-        <v>17624000</v>
+        <v>2191000</v>
       </c>
       <c r="I52" s="3">
-        <v>17406000</v>
+        <v>2271000</v>
       </c>
       <c r="J52" s="3">
+        <v>2116000</v>
+      </c>
+      <c r="K52" s="3">
         <v>17053000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15456000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14296000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13392000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13134000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10502000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>60471000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>55833000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>13447000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11479000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9947000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12088000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9839000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9734000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10179000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10191000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11471000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11031000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10660000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11763000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9787000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8538000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8885000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8984000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9149000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8275000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4902,109 +5024,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>381164000</v>
+      </c>
+      <c r="E54" s="3">
         <v>379146000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>380158000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>380255000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>384830000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>379955000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>377716000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>379680000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>375090000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>370147000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>365716000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>366596000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>353457000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>349190000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>345573000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>316481000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>296994000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>293259000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>294500000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>291727000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>284875000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>283108000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>283947000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>264829000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>265562000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>263303000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>264516000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>257143000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>254682000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>252978000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>246731000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>244180000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>239498000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5040,8 +5168,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5077,614 +5206,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>22222000</v>
+      </c>
+      <c r="E57" s="3">
         <v>19727000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20139000</v>
       </c>
-      <c r="F57" s="3">
-        <v>23453000</v>
-      </c>
       <c r="G57" s="3">
+        <v>10021000</v>
+      </c>
+      <c r="H57" s="3">
         <v>26140000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>20067000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19273000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>23977000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22235000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>20956000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18169000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24833000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20153000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17328000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17219000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20658000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17391000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19297000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17419000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>21806000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>19566000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>17633000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>18664000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>22501000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>19342000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>18560000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>17052000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>21232000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>18434000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>17825000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>14826000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>13876000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>18002000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>23255000</v>
+        <v>27776000</v>
       </c>
       <c r="E58" s="3">
-        <v>15594000</v>
+        <v>29148000</v>
       </c>
       <c r="F58" s="3">
-        <v>12973000</v>
+        <v>21587000</v>
       </c>
       <c r="G58" s="3">
-        <v>12950000</v>
+        <v>17239000</v>
       </c>
       <c r="H58" s="3">
-        <v>14827000</v>
+        <v>18067000</v>
       </c>
       <c r="I58" s="3">
-        <v>12081000</v>
+        <v>19999000</v>
       </c>
       <c r="J58" s="3">
+        <v>17178000</v>
+      </c>
+      <c r="K58" s="3">
         <v>9963000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>14995000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12873000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13421000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7443000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7623000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7023000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8802000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5889000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5770000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6651000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>11175000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>10777000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7830000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>8773000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>8614000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7190000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6502000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>5466000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>6323000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3453000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2180000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1153000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3707000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2645000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3852000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>17824000</v>
+        <v>11818000</v>
       </c>
       <c r="E59" s="3">
-        <v>17898000</v>
+        <v>11931000</v>
       </c>
       <c r="F59" s="3">
-        <v>16797000</v>
+        <v>11905000</v>
       </c>
       <c r="G59" s="3">
-        <v>16587000</v>
+        <v>15143000</v>
       </c>
       <c r="H59" s="3">
-        <v>16510000</v>
+        <v>11470000</v>
       </c>
       <c r="I59" s="3">
-        <v>16414000</v>
+        <v>11338000</v>
       </c>
       <c r="J59" s="3">
+        <v>11317000</v>
+      </c>
+      <c r="K59" s="3">
         <v>16231000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15911000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15395000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14995000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14884000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13582000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15727000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12709000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13113000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13024000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12938000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12463000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12285000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11813000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11808000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11329000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8239000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8323000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8303000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8240000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8352000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8316000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8780000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8131000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>13819000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8444000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>61816000</v>
+      </c>
+      <c r="E60" s="3">
         <v>60806000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53631000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53223000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>55677000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>51404000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>47768000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>50171000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>53141000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>49224000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>46585000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>47160000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>41358000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>40078000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>38730000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>39660000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>36185000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>38886000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>41057000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>44868000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>39209000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>38214000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>38607000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>37930000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>34167000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>32329000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>31615000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>33037000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>28930000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>27758000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>26664000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>30340000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>30298000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>126022000</v>
+        <v>150580000</v>
       </c>
       <c r="E61" s="3">
-        <v>136104000</v>
+        <v>149182000</v>
       </c>
       <c r="F61" s="3">
-        <v>137701000</v>
+        <v>159187000</v>
       </c>
       <c r="G61" s="3">
-        <v>134441000</v>
+        <v>161358000</v>
       </c>
       <c r="H61" s="3">
-        <v>137871000</v>
+        <v>160007000</v>
       </c>
       <c r="I61" s="3">
-        <v>140772000</v>
+        <v>162303000</v>
       </c>
       <c r="J61" s="3">
+        <v>169023000</v>
+      </c>
+      <c r="K61" s="3">
         <v>140676000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>132912000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>136184000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>139961000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>143425000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>143352000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>144894000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>149700000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>123173000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>109790000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>106190000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>106561000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>100712000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>101769000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>104598000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>105045000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>105873000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>106440000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>109174000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>112734000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>113642000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>115317000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>116390000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>112839000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>105433000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>102739000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>94779000</v>
+        <v>10609000</v>
       </c>
       <c r="E62" s="3">
-        <v>94697000</v>
+        <v>10844000</v>
       </c>
       <c r="F62" s="3">
-        <v>95532000</v>
+        <v>10880000</v>
       </c>
       <c r="G62" s="3">
-        <v>95624000</v>
+        <v>10958000</v>
       </c>
       <c r="H62" s="3">
-        <v>94178000</v>
+        <v>11622000</v>
       </c>
       <c r="I62" s="3">
-        <v>94957000</v>
+        <v>11565000</v>
       </c>
       <c r="J62" s="3">
+        <v>8559000</v>
+      </c>
+      <c r="K62" s="3">
         <v>96370000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>100254000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>97382000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>93995000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>92811000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>90258000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>89106000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>84460000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>84376000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>84489000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>84070000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>85229000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>83312000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>83585000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>82349000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>82835000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>66316000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>68868000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>68225000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>67822000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>65777000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>81984000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>82069000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>82191000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>84375000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>84478000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5784,8 +5932,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5885,8 +6036,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5986,109 +6140,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>282974000</v>
+        <v>283496000</v>
       </c>
       <c r="E66" s="3">
-        <v>285824000</v>
+        <v>281607000</v>
       </c>
       <c r="F66" s="3">
-        <v>287825000</v>
+        <v>284432000</v>
       </c>
       <c r="G66" s="3">
-        <v>287089000</v>
+        <v>286456000</v>
       </c>
       <c r="H66" s="3">
-        <v>284762000</v>
+        <v>285742000</v>
       </c>
       <c r="I66" s="3">
-        <v>284833000</v>
+        <v>283453000</v>
       </c>
       <c r="J66" s="3">
+        <v>283497000</v>
+      </c>
+      <c r="K66" s="3">
         <v>288536000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>287622000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>284131000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>281954000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>284806000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>276413000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>275506000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>274341000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>248639000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>231925000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>230562000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>234290000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>230332000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>225954000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>226526000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>228091000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>211684000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>211067000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>211279000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>213735000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>214047000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>227834000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>227789000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>223238000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>221656000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>219038000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6124,8 +6284,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6225,8 +6386,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6326,8 +6490,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6427,8 +6594,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6528,109 +6698,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>86958000</v>
+      </c>
+      <c r="E72" s="3">
         <v>86504000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>84714000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>82915000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>88416000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>86448000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>84543000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>82380000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>78545000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>76401000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>73891000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>71993000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>70062000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>66310000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>63107000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>60464000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>58473000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>56746000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>54557000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>53147000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>50595000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>47945000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>46493000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>43542000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>44091000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>41657000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>39974000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>35635000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19373000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>18159000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>16153000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>15059000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>12918000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6730,8 +6906,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6831,8 +7010,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6932,109 +7114,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>96326000</v>
+      </c>
+      <c r="E76" s="3">
         <v>96172000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>94334000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>92430000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>97741000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>95193000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>92883000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>91144000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>87468000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>86016000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>83762000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>81790000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>77044000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>73684000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>71232000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>67842000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>65069000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>62697000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>60210000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>61395000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>58921000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>56582000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>55856000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>53145000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>54495000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>52024000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>50781000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>43096000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>26848000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>25189000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>23493000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>22524000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>20460000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7134,215 +7322,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3306000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4593000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4602000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2705000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4762000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4648000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4909000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6577000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4900000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5199000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4580000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4613000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6407000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5800000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5245000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4588000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4357000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4700000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4156000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5095000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5194000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3944000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5032000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1939000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4924000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4120000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4545000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>18669000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3620000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4362000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3450000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4495000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7378,109 +7575,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4483000</v>
+        <v>3720000</v>
       </c>
       <c r="E83" s="3">
-        <v>4445000</v>
+        <v>3706000</v>
       </c>
       <c r="F83" s="3">
-        <v>4516000</v>
+        <v>3671000</v>
       </c>
       <c r="G83" s="3">
-        <v>4431000</v>
+        <v>3655000</v>
       </c>
       <c r="H83" s="3">
-        <v>4359000</v>
+        <v>3666000</v>
       </c>
       <c r="I83" s="3">
-        <v>4318000</v>
+        <v>3670000</v>
       </c>
       <c r="J83" s="3">
+        <v>3601000</v>
+      </c>
+      <c r="K83" s="3">
         <v>4218000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4324000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4321000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4236000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4051000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3961000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4020000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4174000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4197000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4192000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4181000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4150000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4105000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4114000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4232000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4231000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4352000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4377000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4350000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4324000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4456000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4272000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4167000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4059000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3987000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7580,8 +7781,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7681,8 +7885,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7782,8 +7989,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7883,8 +8093,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7984,109 +8197,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9911000</v>
+      </c>
+      <c r="E89" s="3">
         <v>9485000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7084000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8677000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10778000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9731000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8289000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8942000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10534000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10844000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6821000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8377000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10724000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10744000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9694000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9296000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8920000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>14728000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8824000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8998000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>10912000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8755000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7081000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8095000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>9811000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>9785000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6648000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8084000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7303000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>8237000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1681000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>5086000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4816000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8122,109 +8341,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-3859000</v>
+        <v>-3948000</v>
       </c>
       <c r="E91" s="3">
-        <v>-4825000</v>
+        <v>-3695000</v>
       </c>
       <c r="F91" s="3">
-        <v>-8540000</v>
+        <v>-4376000</v>
       </c>
       <c r="G91" s="3">
-        <v>-4868000</v>
+        <v>-4603000</v>
       </c>
       <c r="H91" s="3">
-        <v>-4599000</v>
+        <v>-4094000</v>
       </c>
       <c r="I91" s="3">
-        <v>-6556000</v>
+        <v>-4112000</v>
       </c>
       <c r="J91" s="3">
+        <v>-5958000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-8039000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5935000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5107000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7659000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6994000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6894000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4222000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4494000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4024000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4318000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4576000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5274000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5607000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4365000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3699000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4268000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4632000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4188000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3286000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4552000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5965000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4271000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3944000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-6526000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-11570000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-8506000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8324,8 +8547,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8425,109 +8651,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4003000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3865000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5245000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7824000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5408000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4090000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6110000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5342000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8664000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6661000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7995000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10135000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2617000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4748000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-49653000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5043000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6345000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5144000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6980000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5424000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3568000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3786000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4803000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4798000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4408000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3443000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5285000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5469000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3728000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4709000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4550000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-8444000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5192000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8563,109 +8795,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2802000</v>
+        <v>2801000</v>
       </c>
       <c r="E96" s="3">
-        <v>-2796000</v>
+        <v>2802000</v>
       </c>
       <c r="F96" s="3">
-        <v>-2794000</v>
+        <v>2796000</v>
       </c>
       <c r="G96" s="3">
-        <v>-2744000</v>
+        <v>2794000</v>
       </c>
       <c r="H96" s="3">
-        <v>-2743000</v>
+        <v>2744000</v>
       </c>
       <c r="I96" s="3">
-        <v>-2744000</v>
+        <v>2743000</v>
       </c>
       <c r="J96" s="3">
+        <v>2744000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-2739000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2688000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2724000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2654000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2648000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2599000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2597000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2601000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2596000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2546000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2543000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2547000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2542000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2493000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2492000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-2489000</v>
       </c>
       <c r="Z96" s="3">
         <v>-2489000</v>
       </c>
       <c r="AA96" s="3">
-        <v>-2438000</v>
+        <v>-2489000</v>
       </c>
       <c r="AB96" s="3">
         <v>-2438000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-2438000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-2407000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-2405000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-2357000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-2356000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-2354000</v>
       </c>
       <c r="AH96" s="3">
         <v>-2354000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-2354000</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-2303000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8765,8 +9001,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8866,8 +9105,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8967,132 +9209,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4415000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5634000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1428000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3016000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6055000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3203000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2383000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3076000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1616000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4082000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>245000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5192000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3081000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-11406000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>27956000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>9062000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1505000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-8795000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2563000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3863000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6258000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5386000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2657000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2956000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4556000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-6549000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3497000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2765000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>4665000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-203000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>3977000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9169,105 +9417,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1493000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>411000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2163000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-685000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2438000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-204000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>524000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>254000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>101000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-929000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6950000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5026000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5410000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-12003000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>13315000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1070000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>789000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4407000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-289000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1086000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-417000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-379000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>341000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>847000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-207000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>47000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2180000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-56000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>456000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1491000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3584000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>VZ</t>
   </si>
@@ -656,443 +656,455 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>35681000</v>
+      </c>
+      <c r="E8" s="3">
         <v>33330000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>32796000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>32981000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>35130000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>33336000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32596000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32912000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>35251000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>34241000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33789000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33554000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34067000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>32915000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33764000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>32867000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34692000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>31543000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>30447000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>31610000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34775000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>32894000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>32071000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>32128000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>34281000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>32607000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>32203000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>31772000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>33955000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>31717000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>30548000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>29814000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>32340000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>30937000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>15514000</v>
+      </c>
+      <c r="E9" s="3">
         <v>13051000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12471000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12872000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15174000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13377000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12750000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13504000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15762000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14601000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14420000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14350000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14996000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13528000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14255000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13522000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14822000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12334000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11749000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12296000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>15631000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>13384000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12721000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12990000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15291000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13331000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13328000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>13255000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>15387000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>20614000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>12484000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>12047000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>14362000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>12229000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>20167000</v>
+      </c>
+      <c r="E10" s="3">
         <v>20279000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20325000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20109000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19956000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19959000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19846000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19408000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19489000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19640000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19369000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19204000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19071000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19387000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19509000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>19345000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19870000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19209000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>18698000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19314000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19144000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19510000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19350000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>19138000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>18990000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>19276000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>18875000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>18517000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>18568000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>11103000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>18064000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>17767000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>17978000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>18708000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1129,8 +1141,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1233,8 +1246,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1337,216 +1353,225 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-764000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2017000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>47000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4000</v>
       </c>
-      <c r="G14" s="3">
-        <v>7470000</v>
-      </c>
       <c r="H14" s="3">
+        <v>7497000</v>
+      </c>
+      <c r="I14" s="3">
         <v>270000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>323000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-70000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2214000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>645000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>198000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1241000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1230000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>948000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-168000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>223000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>404000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1092000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>255000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1377000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2381000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>291000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1544000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-96000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>4945000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>159000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>910000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>356000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2558000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>620000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-1015000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>722000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-1589000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>797000</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4506000</v>
+      </c>
+      <c r="E15" s="3">
         <v>4458000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4483000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4445000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4516000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4410000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4359000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4318000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4218000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4324000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4321000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4236000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4051000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3961000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4020000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4174000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4197000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4192000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4181000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4150000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4105000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4114000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4232000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4231000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4350000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4370000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4338000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4322000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4237000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>8544000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>12388000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>8118000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>3987000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,216 +1605,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28107000</v>
+      </c>
+      <c r="E17" s="3">
         <v>25353000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25211000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25354000</v>
       </c>
-      <c r="G17" s="3">
-        <v>27955000</v>
-      </c>
       <c r="H17" s="3">
+        <v>27928000</v>
+      </c>
+      <c r="I17" s="3">
         <v>25493000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24971000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25315000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25508000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26992000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>26435000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>26999000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>27689000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24958000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25431000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25097000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>27695000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>24957000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>23341000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25213000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>30127000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>25005000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>25765000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>24323000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>31991000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>24954000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>25586000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>24672000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>30058000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>25183000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>22534000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>23700000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>24317000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>24397000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7574000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7977000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7585000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7627000</v>
       </c>
-      <c r="G18" s="3">
-        <v>7175000</v>
-      </c>
       <c r="H18" s="3">
+        <v>7202000</v>
+      </c>
+      <c r="I18" s="3">
         <v>7843000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7625000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7597000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9743000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7249000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7354000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6555000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6378000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7957000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8333000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7770000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6997000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6586000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7106000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6397000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4648000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7889000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6306000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7805000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2290000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>7653000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>6617000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>7100000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3897000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6534000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>8014000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>6114000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>8023000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>6540000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1826,528 +1858,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E20" s="3">
         <v>83000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-111000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>12000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>46000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>35000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>173000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>208000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>288000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>314000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>505000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1218000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>335000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>409000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>336000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>309000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>197000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>313000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>223000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>180000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>219000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>193000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>276000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>233000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>132000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>155000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>256000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>141000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>171000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>200000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>63000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11876000</v>
+      </c>
+      <c r="E21" s="3">
         <v>12352000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12179000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12073000</v>
       </c>
-      <c r="G21" s="3">
-        <v>11679000</v>
-      </c>
       <c r="H21" s="3">
+        <v>11706000</v>
+      </c>
+      <c r="I21" s="3">
         <v>12207000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11987000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11880000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14134000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11781000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11963000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11105000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10934000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13136000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12688000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12353000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11530000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11087000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>11484000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>10860000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8976000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>12183000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>10757000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>12229000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6918000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>12263000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>11099000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>11579000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8609000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>10947000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>12352000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>10373000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>12073000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>10556000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1644000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1672000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1698000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1635000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1599000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1433000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1285000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1207000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1105000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>937000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>785000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>786000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>739000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>801000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>844000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1101000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1080000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1044000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1116000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1034000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1159000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1146000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1215000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1210000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1199000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1211000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1222000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1201000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1219000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1164000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1218000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1132000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1137000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1038000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6568000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4302000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6034000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6075000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1817000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6192000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6112000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6500000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8811000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6520000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6857000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6083000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6144000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8374000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7824000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7078000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6253000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5851000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6187000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5676000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3712000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6923000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5310000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6788000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1367000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6675000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5527000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6054000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2934000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5511000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>6967000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5182000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>6949000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5576000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1454000</v>
+      </c>
+      <c r="E24" s="3">
         <v>891000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1332000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1353000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>756000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1308000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1346000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1482000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2113000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1496000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1542000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1372000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1407000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1820000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1875000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1700000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1535000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1347000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1348000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1389000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1505000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1586000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1236000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1628000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-698000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1613000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1281000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1388000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>912000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1775000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2489000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1629000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2349000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1829000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2450,216 +2498,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5114000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3411000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4702000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4722000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2573000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4884000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4766000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5018000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6698000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5024000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5315000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4711000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4737000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6554000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5949000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5378000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4718000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4504000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4839000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4287000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5217000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5337000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4074000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5160000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2065000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5062000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4246000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4666000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2022000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3736000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4478000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3553000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4600000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3747000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5005000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3306000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4593000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4602000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2705000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4762000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4648000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4909000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6577000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4900000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5199000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4580000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4613000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6407000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5800000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5245000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4588000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4357000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4700000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4156000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5095000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5194000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3944000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5032000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1939000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4924000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4120000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4545000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1908000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3620000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4362000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3450000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4495000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2762,8 +2819,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2830,17 +2890,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AA29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2848,11 +2908,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>16761000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2866,8 +2926,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2970,8 +3033,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3074,216 +3140,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-204000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-83000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>111000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-12000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-46000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-35000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-173000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-208000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-288000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-314000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-505000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1218000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-335000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-409000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-336000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-309000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-197000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-313000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-223000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-180000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-219000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-193000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-276000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-233000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-132000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-256000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-171000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-200000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-63000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-74000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5005000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3306000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4593000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4602000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2705000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4762000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4648000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4909000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6577000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4900000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5199000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4580000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4613000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6407000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5800000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5245000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4588000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4357000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4700000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4156000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5095000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5194000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3944000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5032000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1939000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4924000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4120000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4545000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>18669000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3620000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4362000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3450000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4495000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3386,221 +3461,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5005000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3306000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4593000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4602000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2705000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4762000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4648000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4909000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6577000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4900000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5199000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4580000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4613000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6407000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5800000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5245000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4588000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4357000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4700000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4156000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5095000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5194000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3944000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5032000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1939000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4924000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4120000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4545000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>18669000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3620000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4362000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3450000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4495000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3637,8 +3721,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3675,138 +3760,142 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4194000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4987000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2432000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2365000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2065000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4210000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4803000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2234000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2605000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2082000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1857000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1661000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2921000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9936000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4657000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10205000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>22171000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8983000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7882000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7047000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2594000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3020000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1949000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2322000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2745000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2538000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1750000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1923000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2079000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4487000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4583000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4307000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2880000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6441000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>26000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>55000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>60000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>100000</v>
-      </c>
-      <c r="I42" s="3">
-        <v>117000</v>
       </c>
       <c r="J42" s="3">
         <v>117000</v>
       </c>
       <c r="K42" s="3">
-        <v>0</v>
+        <v>117000</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -3883,736 +3972,760 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26109000</v>
+      </c>
+      <c r="E43" s="3">
         <v>26523000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>26155000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25860000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>25085000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24143000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>23728000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>23436000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24506000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24362000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24606000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24335000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24585000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>22896000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>22029000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>23236000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>24650000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>23350000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>23434000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>24641000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>26277000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>25531000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>25738000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>25239000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>25859000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>24765000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>23875000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>22595000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>23493000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>21549000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>19771000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>16863000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>17513000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>14832000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2247000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2523000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1841000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2076000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2057000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2240000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1896000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2381000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2388000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3133000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3646000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3659000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3055000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2303000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1421000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1303000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1796000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1457000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1289000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1633000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1422000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1538000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1167000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1417000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1336000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1270000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1102000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1285000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1276000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1116000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1194000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1202000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1318000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5050000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2846000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4613000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4581000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4162000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2675000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4134000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4578000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8358000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10169000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7390000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5925000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6167000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5142000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7519000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4903000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5977000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4782000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4728000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7384000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7180000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4806000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4454000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4419000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4696000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4581000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4149000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5222000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3307000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3555000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3353000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4794000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4800000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3030000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>40523000</v>
+      </c>
+      <c r="E46" s="3">
         <v>40641000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>38056000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>37957000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>36814000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>38119000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37388000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>35722000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>37857000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>39746000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>37499000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35580000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36728000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>40277000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>35626000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>39647000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>54594000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>38572000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>37333000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>40705000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>37473000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>34895000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>33308000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>33397000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>34636000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>33154000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>30876000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>31025000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>29913000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>30867000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>28823000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>27158000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>26395000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>25621000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1111000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1142000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1179000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1211000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1214000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1176000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1305000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1360000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1278000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1260000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1296000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1263000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1256000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1277000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>760000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>749000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>793000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>725000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>760000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>834000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>860000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>912000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>897000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>925000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>917000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>976000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1070000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>994000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1039000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1054000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1075000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1080000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1110000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1119000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>132994000</v>
+      </c>
+      <c r="E48" s="3">
         <v>131141000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>131954000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>132214000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>133036000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>132576000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>132615000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>132934000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>133564000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>129592000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>128408000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>127337000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>127579000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>123725000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>122382000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>117191000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>117364000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>115862000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>115185000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>114649000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>114609000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>111067000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>110285000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>110954000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>89286000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>87464000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>87781000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>87922000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>88568000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>86622000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>86521000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>85213000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>84751000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>83414000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>190583000</v>
+      </c>
+      <c r="E49" s="3">
         <v>189999000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>189813000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>189788000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>189567000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>195059000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>191081000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>190405000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>189928000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>189036000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>188648000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>188144000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>187899000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>177676000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>129951000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>132153000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>130283000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>130356000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>130034000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>126224000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>128946000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>128267000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>128439000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>128480000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>128519000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>132937000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>132916000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>132812000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>127836000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>127601000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>127674000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>124296000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>122775000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>121069000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4715,8 +4828,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4819,112 +4935,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2494000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2622000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2324000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2483000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2593000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2191000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2271000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2116000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17053000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15456000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14296000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13392000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13134000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10502000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>60471000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>55833000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>13447000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11479000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9947000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12088000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9839000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9734000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10179000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10191000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11471000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11031000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10660000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>11763000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9787000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8538000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8885000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8984000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9149000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>8275000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5027,112 +5149,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>384711000</v>
+      </c>
+      <c r="E54" s="3">
         <v>381164000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>379146000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>380158000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>380255000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>384830000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>379955000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>377716000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>379680000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>375090000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>370147000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>365716000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>366596000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>353457000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>349190000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>345573000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>316481000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>296994000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>293259000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>294500000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>291727000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>284875000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>283108000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>283947000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>264829000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>265562000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>263303000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>264516000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>257143000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>254682000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>252978000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>246731000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>244180000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>239498000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5169,8 +5297,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5207,632 +5336,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10425000</v>
+      </c>
+      <c r="E57" s="3">
         <v>22222000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19727000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20139000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10021000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>26140000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>20067000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19273000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23977000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22235000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>20956000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18169000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>24833000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>20153000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17328000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17219000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>20658000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>17391000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>19297000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>17419000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>21806000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>19566000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>17633000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>18664000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>22501000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>19342000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>18560000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>17052000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>21232000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>18434000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>17825000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>14826000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>13876000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>18002000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>27048000</v>
+      </c>
+      <c r="E58" s="3">
         <v>27776000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>29148000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>21587000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17239000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18067000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19999000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17178000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9963000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14995000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12873000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13421000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7443000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7623000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7023000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>8802000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5889000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5770000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6651000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>11175000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>10777000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7830000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>8773000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>8614000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7190000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6502000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>5466000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>6323000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3453000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2180000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1153000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3707000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2645000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3852000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16251000</v>
+      </c>
+      <c r="E59" s="3">
         <v>11818000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11931000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11905000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15143000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11470000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11338000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11317000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16231000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15911000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15395000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14995000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14884000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13582000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15727000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12709000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13113000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13024000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12938000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12463000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12285000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11813000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11808000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11329000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8239000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8323000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8303000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8240000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8352000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8316000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8780000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8131000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>13819000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>8444000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>64771000</v>
+      </c>
+      <c r="E60" s="3">
         <v>61816000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>60806000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53631000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>53223000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>55677000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>51404000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>47768000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>50171000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>53141000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>49224000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>46585000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>47160000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>41358000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>40078000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>38730000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>39660000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>36185000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38886000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>41057000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>44868000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>39209000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>38214000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>38607000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>37930000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>34167000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>32329000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>31615000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>33037000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>28930000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>27758000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>26664000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>30340000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>30298000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>144647000</v>
+      </c>
+      <c r="E61" s="3">
         <v>150580000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>149182000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>159187000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>161358000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>160007000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>162303000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>169023000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>140676000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>132912000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>136184000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>139961000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>143425000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>143352000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>144894000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>149700000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>123173000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>109790000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>106190000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>106561000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>100712000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>101769000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>104598000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>105045000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>105873000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>106440000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>109174000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>112734000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>113642000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>115317000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>116390000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>112839000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>105433000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>102739000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13803000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10609000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10844000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10880000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10958000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11622000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11565000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8559000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>96370000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>100254000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>97382000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>93995000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>92811000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>90258000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>89106000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>84460000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>84376000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>84489000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>84070000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>85229000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>83312000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>83585000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>82349000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>82835000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>66316000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>68868000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>68225000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>67822000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>65777000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>81984000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>82069000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>82191000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>84375000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>84478000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5935,8 +6083,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6039,8 +6190,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6143,112 +6297,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>284136000</v>
+      </c>
+      <c r="E66" s="3">
         <v>283496000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>281607000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>284432000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>286456000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>285742000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>283453000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>283497000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>288536000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>287622000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>284131000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>281954000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>284806000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>276413000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>275506000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>274341000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>248639000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>231925000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>230562000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>234290000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>230332000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>225954000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>226526000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>228091000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>211684000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>211067000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>211279000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>213735000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>214047000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>227834000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>227789000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>223238000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>221656000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>219038000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6285,8 +6445,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6389,8 +6550,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6493,8 +6657,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6597,8 +6764,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6701,112 +6871,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>89110000</v>
+      </c>
+      <c r="E72" s="3">
         <v>86958000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>86504000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>84714000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>82915000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>88416000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>86448000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>84543000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>82380000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>78545000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>76401000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>73891000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>71993000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>70062000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>66310000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>63107000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>60464000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>58473000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>56746000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>54557000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>53147000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>50595000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>47945000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>46493000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>43542000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>44091000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>41657000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>39974000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>35635000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19373000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18159000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>16153000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>15059000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>12918000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6909,8 +7085,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7013,8 +7192,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7117,112 +7299,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>99237000</v>
+      </c>
+      <c r="E76" s="3">
         <v>96326000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>96172000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>94334000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>92430000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>97741000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>95193000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>92883000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>91144000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>87468000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>86016000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>83762000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>81790000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>77044000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>73684000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>71232000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>67842000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>65069000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>62697000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>60210000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>61395000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>58921000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>56582000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>55856000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>53145000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>54495000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>52024000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>50781000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>43096000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>26848000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>25189000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>23493000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>22524000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>20460000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7325,221 +7513,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5005000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3306000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4593000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4602000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2705000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4762000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4648000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4909000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6577000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4900000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5199000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4580000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4613000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6407000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5800000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5245000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4588000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4357000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4700000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4156000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5095000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5194000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3944000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5032000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1939000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4924000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4120000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4545000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>18669000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3620000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4362000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3450000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4495000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7576,112 +7773,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4516000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3720000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3706000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3671000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3655000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3666000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3670000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3601000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4218000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4324000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4321000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4236000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4051000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3961000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4020000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4174000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4197000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4192000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4181000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4150000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4105000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4114000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4232000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4231000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4352000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4377000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4350000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4324000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4456000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4272000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4167000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4059000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>3987000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7784,8 +7985,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7888,8 +8092,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7992,8 +8199,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8096,8 +8306,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8200,112 +8413,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10432000</v>
+      </c>
+      <c r="E89" s="3">
         <v>9911000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9485000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7084000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8677000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10778000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9731000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8289000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8942000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10534000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10844000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6821000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8377000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10724000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10744000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9694000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9296000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8920000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>14728000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8824000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8998000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>10912000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8755000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>7081000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8095000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>9811000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>9785000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6648000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>8084000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7303000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>8237000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1681000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>5086000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>4816000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8342,112 +8561,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5071000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3948000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3695000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4376000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4603000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4094000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4112000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5958000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8039000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5935000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5107000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7659000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6994000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6894000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4222000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4494000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4024000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4318000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4576000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5274000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5607000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4365000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3699000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4268000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4632000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4188000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3286000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4552000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5965000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4271000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3944000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-6526000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-11570000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-8506000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8550,8 +8773,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8654,112 +8880,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5561000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4003000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3865000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5245000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7824000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5408000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4090000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6110000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5342000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8664000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6661000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7995000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10135000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2617000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4748000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-49653000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5043000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6345000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5144000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6980000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5424000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3568000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3786000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4803000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4798000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4408000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3443000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5285000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5469000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3728000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4709000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4550000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-8444000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-5192000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8796,112 +9028,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2850000</v>
+      </c>
+      <c r="E96" s="3">
         <v>2801000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2802000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2796000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2794000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2744000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2743000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2744000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2739000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2688000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2724000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2654000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2648000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2599000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2597000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2601000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2596000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2546000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2543000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2547000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2542000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2493000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-2492000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-2489000</v>
       </c>
       <c r="AA96" s="3">
         <v>-2489000</v>
       </c>
       <c r="AB96" s="3">
-        <v>-2438000</v>
+        <v>-2489000</v>
       </c>
       <c r="AC96" s="3">
         <v>-2438000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-2438000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-2407000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-2405000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-2357000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-2356000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-2354000</v>
       </c>
       <c r="AI96" s="3">
         <v>-2354000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-2354000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-2303000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9004,8 +9240,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9108,8 +9347,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9212,112 +9454,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5623000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4415000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5634000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1428000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3016000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6055000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3203000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2383000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3076000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1616000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4082000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>245000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5192000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3081000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-11406000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>27956000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>9062000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1505000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-8795000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2563000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3863000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6258000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5386000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2657000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2956000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4556000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-6549000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3497000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2765000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>4665000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-203000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>3977000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9342,8 +9590,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9420,108 +9668,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-752000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1493000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>411000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2163000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-685000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2438000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-204000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>524000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>254000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>101000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-929000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6950000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5026000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5410000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12003000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>13315000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1070000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>789000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4407000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-289000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1086000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-417000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-379000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>341000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>847000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-207000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>47000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2180000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-56000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>456000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1491000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>3584000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>VZ</t>
   </si>
@@ -656,455 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>33485000</v>
+      </c>
+      <c r="E8" s="3">
         <v>35681000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33330000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>32796000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32981000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>35130000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33336000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32596000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>32912000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>35251000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>34241000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33789000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33554000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34067000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>32915000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>33764000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>32867000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34692000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>31543000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>30447000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>31610000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>34775000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>32894000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>32071000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>32128000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>34281000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>32607000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>32203000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>31772000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>33955000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>31717000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>30548000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>29814000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>32340000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>30937000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13056000</v>
+      </c>
+      <c r="E9" s="3">
         <v>15514000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13051000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12471000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12872000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15174000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13377000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12750000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13504000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15762000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14601000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14420000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14350000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14996000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13528000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14255000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13522000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14822000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12334000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11749000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12296000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15631000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13384000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12721000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12990000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15291000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13331000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>13328000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>13255000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>15387000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>20614000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>12484000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>12047000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>14362000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>12229000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>20429000</v>
+      </c>
+      <c r="E10" s="3">
         <v>20167000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20279000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20325000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20109000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19956000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19959000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19846000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19408000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19489000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19640000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19369000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19204000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19071000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19387000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>19509000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19345000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19870000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19209000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>18698000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19314000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19144000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19510000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>19350000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>19138000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>18990000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>19276000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>18875000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>18517000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>18568000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>11103000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>18064000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>17767000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>17978000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>18708000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1249,8 +1262,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1356,222 +1372,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-764000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2017000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>47000</v>
       </c>
-      <c r="G14" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H14" s="3">
+        <v>217000</v>
+      </c>
+      <c r="I14" s="3">
         <v>7497000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>270000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>323000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-70000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2214000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>645000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>198000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1241000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1230000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>948000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-168000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>223000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>404000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1092000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>255000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1377000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2381000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>291000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1544000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-96000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>4945000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>159000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>910000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>356000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2558000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>620000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-1015000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>722000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-1589000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>797000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4387000</v>
+      </c>
+      <c r="E15" s="3">
         <v>4506000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4458000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4483000</v>
       </c>
-      <c r="G15" s="3">
-        <v>4445000</v>
-      </c>
       <c r="H15" s="3">
+        <v>4224000</v>
+      </c>
+      <c r="I15" s="3">
         <v>4516000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4410000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4359000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4318000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4218000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4324000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4321000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4236000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4051000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3961000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4020000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4174000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4197000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4192000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4181000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4150000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4105000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4114000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4232000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4231000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4350000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4370000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4338000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4322000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4237000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>8544000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>12388000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>8118000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>3987000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,222 +1631,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25223000</v>
+      </c>
+      <c r="E17" s="3">
         <v>28107000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25353000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25211000</v>
       </c>
-      <c r="G17" s="3">
-        <v>25354000</v>
-      </c>
       <c r="H17" s="3">
+        <v>25133000</v>
+      </c>
+      <c r="I17" s="3">
         <v>27928000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25493000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24971000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25315000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25508000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>26992000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>26435000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26999000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27689000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24958000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25431000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>25097000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>27695000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>24957000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>23341000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>25213000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>30127000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>25005000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>25765000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24323000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>31991000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>24954000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>25586000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>24672000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>30058000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>25183000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>22534000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>23700000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>24317000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>24397000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8262000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7574000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7977000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7585000</v>
       </c>
-      <c r="G18" s="3">
-        <v>7627000</v>
-      </c>
       <c r="H18" s="3">
+        <v>7848000</v>
+      </c>
+      <c r="I18" s="3">
         <v>7202000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7843000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7625000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7597000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9743000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7249000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7354000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6555000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6378000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7957000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8333000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7770000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6997000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6586000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7106000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6397000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4648000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>7889000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6306000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7805000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2290000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>7653000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>6617000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>7100000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3897000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6534000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>8014000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>6114000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>8023000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>6540000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1859,543 +1891,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E20" s="3">
         <v>204000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>83000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-111000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>12000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>46000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>35000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>173000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>208000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>288000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>314000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>505000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1218000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>335000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>409000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>336000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>309000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>197000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>313000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>223000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>180000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>219000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>193000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>276000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>233000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>132000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>155000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>256000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>141000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>171000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>200000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>63000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12529000</v>
+      </c>
+      <c r="E21" s="3">
         <v>11876000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12352000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12179000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12073000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11706000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12207000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11987000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11880000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14134000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11781000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11963000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11105000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10934000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13136000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12688000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12353000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11530000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>11087000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11484000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>10860000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8976000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>12183000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>10757000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>12229000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6918000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>12263000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>11099000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>11579000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>8609000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>10947000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>12352000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>10373000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>12073000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>10556000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1632000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1644000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1672000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1698000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1635000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1599000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1433000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1285000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1207000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1105000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>937000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>785000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>786000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>739000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>801000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>844000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1101000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1080000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1044000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1116000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1034000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1159000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1146000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1215000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1210000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1199000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1211000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1222000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1201000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1219000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1164000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1218000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1132000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1137000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1038000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6473000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6568000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4302000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6034000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6075000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1817000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6192000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6112000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6500000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8811000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6520000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6857000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6083000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6144000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8374000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7824000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7078000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6253000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5851000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6187000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5676000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3712000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6923000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5310000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6788000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1367000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6675000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5527000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6054000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2934000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5511000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>6967000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>5182000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>6949000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>5576000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1490000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1454000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>891000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1332000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1353000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>756000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1308000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1346000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1482000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2113000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1496000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1542000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1372000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1407000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1820000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1875000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1700000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1535000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1347000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1348000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1389000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1505000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1586000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1236000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1628000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-698000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1613000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1281000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1388000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>912000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1775000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2489000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1629000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2349000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1829000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2501,222 +2549,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4983000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5114000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3411000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4702000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4722000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2573000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4884000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4766000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5018000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6698000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5024000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5315000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4711000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4737000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6554000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5949000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5378000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4718000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4504000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4839000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4287000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5217000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5337000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4074000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5160000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2065000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5062000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4246000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4666000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2022000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3736000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4478000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3553000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4600000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3747000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4879000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5005000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3306000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4593000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4602000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2705000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4762000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4648000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4909000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6577000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4900000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5199000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4580000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4613000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6407000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5800000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5245000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4588000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4357000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4700000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4156000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5095000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5194000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3944000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5032000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1939000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4924000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4120000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4545000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1908000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3620000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4362000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3450000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4495000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2822,8 +2879,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2893,17 +2953,17 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
+      <c r="AB29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2911,11 +2971,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>16761000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2929,8 +2989,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3036,8 +3099,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3143,222 +3209,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-120000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-204000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-83000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>111000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-12000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-46000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-35000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-173000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-208000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-288000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-314000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-505000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1218000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-335000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-409000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-336000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-309000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-197000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-313000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-223000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-180000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-219000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-193000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-276000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-233000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-132000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-256000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-171000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-200000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-63000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-74000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4879000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5005000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3306000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4593000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4602000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2705000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4762000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4648000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4909000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6577000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4900000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5199000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4580000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4613000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6407000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5800000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5245000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4588000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4357000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4700000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4156000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5095000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5194000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3944000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5032000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1939000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4924000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4120000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4545000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>18669000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3620000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4362000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3450000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4495000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3464,227 +3539,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4879000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5005000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3306000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4593000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4602000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2705000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4762000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4648000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4909000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6577000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4900000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5199000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4580000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4613000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6407000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5800000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5245000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4588000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4357000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4700000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4156000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5095000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5194000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3944000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5032000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1939000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4924000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4120000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4545000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>18669000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3620000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4362000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3450000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4495000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3722,8 +3806,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3761,144 +3846,148 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2257000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4194000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4987000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2432000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2365000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2065000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4210000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4803000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2234000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2605000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2082000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1857000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1661000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2921000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9936000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4657000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10205000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>22171000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8983000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7882000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7047000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2594000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3020000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1949000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2322000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2745000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2538000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1750000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1923000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2079000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4487000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4583000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4307000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2880000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>6441000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>26000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>55000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>60000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>100000</v>
-      </c>
-      <c r="J42" s="3">
-        <v>117000</v>
       </c>
       <c r="K42" s="3">
         <v>117000</v>
       </c>
       <c r="L42" s="3">
-        <v>0</v>
+        <v>117000</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -3975,757 +4064,781 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26448000</v>
+      </c>
+      <c r="E43" s="3">
         <v>26109000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>26523000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26155000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>25860000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>25085000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24143000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>23728000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23436000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24506000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24362000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24606000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24335000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24585000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>22896000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>22029000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>23236000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>24650000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>23350000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>23434000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>24641000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>26277000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>25531000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>25738000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>25239000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>25859000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>24765000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>23875000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>22595000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>23493000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>21549000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>19771000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>16863000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>17513000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>14832000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2197000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2247000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2523000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1841000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2076000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2057000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2240000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1896000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2381000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2388000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3133000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3646000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3659000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3055000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2303000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1421000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1303000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1796000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1457000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1289000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1633000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1422000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1538000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1167000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1417000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1336000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1270000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1102000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1285000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1276000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1116000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1194000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1202000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1318000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4587000</v>
+      </c>
+      <c r="E45" s="3">
         <v>5050000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2846000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4613000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4581000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4162000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2675000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4134000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4578000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8358000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10169000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7390000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5925000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6167000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5142000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7519000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4903000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5977000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4782000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4728000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7384000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7180000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4806000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4454000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4419000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4696000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4581000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4149000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5222000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3307000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3555000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3353000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4794000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4800000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3030000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>37353000</v>
+      </c>
+      <c r="E46" s="3">
         <v>40523000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>40641000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38056000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>37957000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>36814000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>38119000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37388000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>35722000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>37857000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>39746000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>37499000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>35580000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>36728000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>40277000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>35626000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>39647000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>54594000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>38572000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>37333000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>40705000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>37473000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>34895000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>33308000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>33397000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>34636000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>33154000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>30876000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>31025000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>29913000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>30867000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>28823000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>27158000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>26395000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>25621000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1127000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1111000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1142000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1179000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1211000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1214000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1176000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1305000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1360000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1278000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1260000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1296000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1263000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1256000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1277000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>760000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>749000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>793000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>725000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>760000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>834000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>860000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>912000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>897000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>925000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>917000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>976000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1070000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>994000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1039000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1054000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1075000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1080000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1110000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1119000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>132098000</v>
+      </c>
+      <c r="E48" s="3">
         <v>132994000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>131141000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>131954000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>132214000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>133036000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>132576000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>132615000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>132934000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>133564000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>129592000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>128408000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>127337000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>127579000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>123725000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>122382000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>117191000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>117364000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>115862000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>115185000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>114649000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>114609000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>111067000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>110285000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>110954000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>89286000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>87464000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>87781000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>87922000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>88568000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>86622000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>86521000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>85213000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>84751000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>83414000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>190415000</v>
+      </c>
+      <c r="E49" s="3">
         <v>190583000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>189999000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>189813000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>189788000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>189567000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>195059000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>191081000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>190405000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>189928000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>189036000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>188648000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>188144000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>187899000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>177676000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>129951000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>132153000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>130283000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>130356000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>130034000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>126224000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>128946000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>128267000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>128439000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>128480000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>128519000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>132937000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>132916000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>132812000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>127836000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>127601000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>127674000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>124296000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>122775000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>121069000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4831,8 +4944,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4938,115 +5054,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2717000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2494000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2622000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2324000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2483000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2593000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2191000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2271000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2116000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17053000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15456000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14296000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13392000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13134000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10502000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>60471000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>55833000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>13447000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11479000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9947000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12088000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9839000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9734000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10179000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10191000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11471000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11031000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10660000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11763000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9787000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8538000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8885000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8984000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9149000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>8275000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5152,115 +5274,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>380364000</v>
+      </c>
+      <c r="E54" s="3">
         <v>384711000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>381164000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>379146000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>380158000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>380255000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>384830000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>379955000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>377716000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>379680000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>375090000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>370147000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>365716000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>366596000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>353457000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>349190000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>345573000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>316481000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>296994000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>293259000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>294500000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>291727000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>284875000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>283108000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>283947000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>264829000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>265562000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>263303000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>264516000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>257143000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>254682000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>252978000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>246731000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>244180000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>239498000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5298,8 +5426,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5337,650 +5466,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19413000</v>
+      </c>
+      <c r="E57" s="3">
         <v>10425000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>22222000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19727000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20139000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10021000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>26140000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>20067000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19273000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>23977000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22235000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>20956000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18169000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>24833000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>20153000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17328000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17219000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>20658000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17391000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>19297000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>17419000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>21806000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>19566000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>17633000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>18664000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>22501000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>19342000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>18560000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>17052000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>21232000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>18434000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>17825000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>14826000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>13876000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>18002000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>29248000</v>
+      </c>
+      <c r="E58" s="3">
         <v>27048000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>27776000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>29148000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>21587000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17239000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18067000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>19999000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17178000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9963000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14995000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12873000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13421000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7443000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7623000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7023000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>8802000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5889000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5770000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6651000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>11175000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>10777000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7830000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>8773000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>8614000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7190000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>6502000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>5466000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>6323000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3453000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2180000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1153000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3707000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2645000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3852000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12405000</v>
+      </c>
+      <c r="E59" s="3">
         <v>16251000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11818000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11931000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11905000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15143000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11470000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11338000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11317000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16231000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15911000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15395000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14995000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14884000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13582000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15727000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12709000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13113000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13024000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12938000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12463000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12285000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11813000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11808000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>11329000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8239000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8323000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8303000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8240000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8352000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8316000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8780000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8131000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>13819000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>8444000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>61066000</v>
+      </c>
+      <c r="E60" s="3">
         <v>64771000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>61816000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>60806000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>53631000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53223000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>55677000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>51404000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>47768000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>50171000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>53141000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>49224000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>46585000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>47160000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>41358000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>40078000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>38730000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>39660000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>36185000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38886000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>41057000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>44868000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>39209000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>38214000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>38607000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>37930000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>34167000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>32329000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>31615000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>33037000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>28930000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>27758000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>26664000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>30340000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>30298000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>143285000</v>
+      </c>
+      <c r="E61" s="3">
         <v>144647000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>150580000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>149182000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>159187000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>161358000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>160007000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>162303000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>169023000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>140676000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>132912000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>136184000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>139961000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>143425000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>143352000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>144894000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>149700000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>123173000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>109790000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>106190000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>106561000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>100712000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>101769000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>104598000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>105045000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>105873000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>106440000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>109174000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>112734000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>113642000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>115317000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>116390000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>112839000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>105433000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>102739000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13362000</v>
+      </c>
+      <c r="E62" s="3">
         <v>13803000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10609000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10844000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10880000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10958000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11622000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11565000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8559000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>96370000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>100254000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>97382000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>93995000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>92811000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>90258000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>89106000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>84460000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>84376000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>84489000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>84070000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>85229000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>83312000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>83585000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>82349000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>82835000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>66316000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>68868000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>68225000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>67822000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>65777000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>81984000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>82069000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>82191000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>84375000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>84478000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6086,8 +6234,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6193,8 +6344,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6300,115 +6454,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>278327000</v>
+      </c>
+      <c r="E66" s="3">
         <v>284136000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>283496000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>281607000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>284432000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>286456000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>285742000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>283453000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>283497000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>288536000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>287622000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>284131000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>281954000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>284806000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>276413000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>275506000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>274341000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>248639000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>231925000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>230562000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>234290000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>230332000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>225954000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>226526000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>228091000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>211684000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>211067000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>211279000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>213735000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>214047000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>227834000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>227789000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>223238000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>221656000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>219038000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6446,8 +6606,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6553,8 +6714,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6660,8 +6824,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6767,8 +6934,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6874,115 +7044,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>91128000</v>
+      </c>
+      <c r="E72" s="3">
         <v>89110000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>86958000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>86504000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>84714000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>82915000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>88416000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>86448000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>84543000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>82380000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>78545000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>76401000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>73891000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>71993000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>70062000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>66310000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>63107000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>60464000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>58473000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>56746000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>54557000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>53147000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>50595000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>47945000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>46493000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>43542000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>44091000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>41657000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>39974000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>35635000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>19373000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>18159000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>16153000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>15059000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>12918000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7088,8 +7264,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7195,8 +7374,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7302,115 +7484,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>100722000</v>
+      </c>
+      <c r="E76" s="3">
         <v>99237000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>96326000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>96172000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>94334000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>92430000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>97741000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>95193000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>92883000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>91144000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>87468000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>86016000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>83762000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>81790000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>77044000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>73684000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>71232000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>67842000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>65069000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>62697000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>60210000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>61395000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>58921000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>56582000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>55856000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>53145000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>54495000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>52024000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>50781000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>43096000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>26848000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>25189000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>23493000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>22524000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>20460000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7516,227 +7704,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4879000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5005000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3306000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4593000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4602000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2705000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4762000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4648000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4909000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6577000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4900000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5199000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4580000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4613000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6407000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5800000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5245000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4588000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4357000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4700000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4156000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5095000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5194000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3944000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5032000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1939000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4924000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4120000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4545000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>18669000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3620000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4362000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3450000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4495000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7774,115 +7971,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3747000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4516000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3720000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3706000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3671000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3655000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3666000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3670000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3601000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4218000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4324000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4321000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4236000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4051000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3961000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4020000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4174000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4197000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4192000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4181000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4150000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4105000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4114000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4232000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4231000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4352000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4377000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4350000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4324000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4456000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4272000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4167000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>4059000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>3987000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7988,8 +8189,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8095,8 +8299,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8202,8 +8409,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8309,8 +8519,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8416,115 +8629,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7782000</v>
+      </c>
+      <c r="E89" s="3">
         <v>10432000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9911000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9485000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7084000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8677000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10778000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9731000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8289000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8942000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10534000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10844000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6821000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8377000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10724000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10744000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9694000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9296000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8920000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>14728000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8824000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8998000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>10912000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8755000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7081000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8095000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>9811000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>9785000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6648000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>8084000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>7303000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>8237000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1681000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>5086000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>4816000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8562,115 +8781,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4145000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5071000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3948000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3695000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4376000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4603000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4094000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4112000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5958000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8039000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5935000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5107000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7659000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6994000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6894000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4222000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4494000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4024000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4318000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4576000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5274000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5607000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4365000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3699000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4268000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4632000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4188000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3286000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4552000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5965000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4271000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3944000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-6526000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-11570000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-8506000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8776,8 +8999,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8883,115 +9109,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3752000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5561000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4003000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3865000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5245000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7824000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5408000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4090000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6110000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5342000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8664000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6661000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7995000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10135000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2617000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4748000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-49653000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5043000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6345000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5144000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6980000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5424000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3568000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3786000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4803000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4798000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4408000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3443000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5285000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5469000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3728000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4709000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-4550000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-8444000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-5192000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9029,115 +9261,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2856000</v>
+      </c>
+      <c r="E96" s="3">
         <v>2850000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2801000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2802000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2796000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2794000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2744000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2743000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2744000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2739000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2688000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2724000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2654000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2648000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2599000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2597000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2601000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2596000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2546000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2543000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2547000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2542000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-2493000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-2492000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-2489000</v>
       </c>
       <c r="AB96" s="3">
         <v>-2489000</v>
       </c>
       <c r="AC96" s="3">
-        <v>-2438000</v>
+        <v>-2489000</v>
       </c>
       <c r="AD96" s="3">
         <v>-2438000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-2438000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-2407000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-2405000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-2357000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-2356000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-2354000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-2354000</v>
       </c>
       <c r="AK96" s="3">
+        <v>-2354000</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-2303000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9243,8 +9479,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9350,8 +9589,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9457,115 +9699,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5893000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5623000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4415000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5634000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1428000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3016000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6055000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3203000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2383000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3076000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1616000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4082000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>245000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5192000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3081000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-11406000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>27956000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>9062000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1505000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-8795000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2563000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3863000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6258000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5386000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2657000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2956000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4556000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-6549000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3497000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2765000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>4665000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-203000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>3977000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9593,8 +9841,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9671,111 +9919,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1863000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-752000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1493000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>411000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2163000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-685000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2438000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-204000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>524000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>254000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>101000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-929000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6950000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5026000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5410000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12003000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13315000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1070000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>789000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4407000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-289000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1086000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-417000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-379000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>341000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>847000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-207000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>47000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2180000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-56000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>456000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1491000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>3584000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>VZ</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>34504000</v>
+      </c>
+      <c r="E8" s="3">
         <v>33485000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35681000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>33330000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32796000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>32981000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>35130000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33336000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>32596000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32912000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>35251000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34241000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33789000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33554000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34067000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>32915000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>33764000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>32867000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>34692000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>31543000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>30447000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>31610000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>34775000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>32894000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>32071000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>32128000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>34281000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>32607000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>32203000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>31772000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>33955000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>31717000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>30548000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>29814000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>32340000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>30937000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13885000</v>
+      </c>
+      <c r="E9" s="3">
         <v>13056000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15514000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13051000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12471000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12872000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15174000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13377000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12750000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13504000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15762000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14601000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14420000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14350000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14996000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13528000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14255000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13522000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14822000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12334000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11749000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12296000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>15631000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13384000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12721000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>12990000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>15291000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>13331000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>13328000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>13255000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>15387000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>20614000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>12484000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>12047000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>14362000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>12229000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>20619000</v>
+      </c>
+      <c r="E10" s="3">
         <v>20429000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20167000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20279000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20325000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>20109000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19956000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19959000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19846000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19408000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19489000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19640000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19369000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19204000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19071000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>19387000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19509000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19345000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19870000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19209000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>18698000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19314000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19144000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>19510000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>19350000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>19138000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>18990000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>19276000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>18875000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>18517000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>18568000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>11103000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>18064000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>17767000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>17978000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>18708000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1155,8 +1167,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1265,8 +1278,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1375,228 +1391,237 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-88000</v>
+      </c>
+      <c r="E14" s="3">
         <v>100000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-764000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2017000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>47000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>217000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7497000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>270000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>323000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-70000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-2214000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>645000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>198000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1241000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1230000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>948000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-168000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>223000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>404000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1092000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>255000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1377000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2381000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>291000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1544000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-96000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>4945000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>159000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>910000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>356000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2558000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>620000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-1015000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>722000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-1589000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>797000</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4635000</v>
+      </c>
+      <c r="E15" s="3">
         <v>4387000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4506000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4458000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4483000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4224000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4516000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4410000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4359000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4318000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4218000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4324000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4321000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4236000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4051000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3961000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4020000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4174000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4197000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4192000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4181000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4150000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4105000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4114000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4232000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4231000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4350000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4370000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4338000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4322000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4237000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>8544000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>12388000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>8118000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>3987000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1632,228 +1657,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>26470000</v>
+      </c>
+      <c r="E17" s="3">
         <v>25223000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28107000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25353000</v>
       </c>
-      <c r="G17" s="3">
-        <v>25211000</v>
-      </c>
       <c r="H17" s="3">
+        <v>25347000</v>
+      </c>
+      <c r="I17" s="3">
         <v>25133000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27928000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25493000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24971000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25315000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25508000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>26992000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26435000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26999000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27689000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>24958000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>25431000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25097000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>27695000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>24957000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>23341000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>25213000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>30127000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>25005000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>25765000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>24323000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>31991000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>24954000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>25586000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>24672000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>30058000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>25183000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>22534000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>23700000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>24317000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>24397000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8034000</v>
+      </c>
+      <c r="E18" s="3">
         <v>8262000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7574000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7977000</v>
       </c>
-      <c r="G18" s="3">
-        <v>7585000</v>
-      </c>
       <c r="H18" s="3">
+        <v>7449000</v>
+      </c>
+      <c r="I18" s="3">
         <v>7848000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7202000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7843000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7625000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7597000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9743000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7249000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7354000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6555000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6378000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7957000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8333000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7770000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6997000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6586000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7106000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6397000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4648000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7889000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6306000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>7805000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2290000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>7653000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>6617000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>7100000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3897000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>6534000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>8014000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>6114000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>8023000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>6540000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1892,558 +1924,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E20" s="3">
         <v>120000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>204000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>83000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-111000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-247000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>46000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>35000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>173000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>208000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>288000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>314000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>505000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1218000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>335000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>409000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>336000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>309000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>197000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>313000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>223000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>180000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>219000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>193000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>276000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>233000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>132000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>155000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>256000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>141000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>171000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>200000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>63000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12740000</v>
+      </c>
+      <c r="E21" s="3">
         <v>12529000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11876000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12352000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12179000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12073000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11706000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12207000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11987000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11880000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14134000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11781000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11963000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11105000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>10934000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13136000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12688000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12353000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>11530000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11087000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>11484000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>10860000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>8976000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>12183000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>10757000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>12229000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>6918000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>12263000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>11099000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>11579000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>8609000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>10947000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>12352000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>10373000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>12073000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>10556000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1639000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1632000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1644000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1672000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1698000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1635000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1599000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1433000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1285000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1207000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1105000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>937000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>785000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>786000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>739000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>801000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>844000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1101000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1080000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1044000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1116000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1034000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1159000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1146000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1215000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1210000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1199000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1211000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1222000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1201000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1219000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1164000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1218000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1132000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1137000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>1038000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6609000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6473000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6568000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4302000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6034000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6075000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1817000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6192000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6112000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6500000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8811000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6520000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6857000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6083000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6144000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8374000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7824000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7078000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6253000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5851000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6187000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5676000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3712000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6923000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5310000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6788000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1367000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6675000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5527000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>6054000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2934000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5511000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>6967000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5182000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>6949000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>5576000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1488000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1490000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1454000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>891000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1332000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1353000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>756000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1308000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1346000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1482000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2113000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1496000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1542000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1372000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1407000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1820000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1875000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1700000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1535000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1347000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1348000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1389000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1505000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1586000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1236000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1628000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-698000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1613000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1281000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1388000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>912000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1775000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2489000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1629000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>2349000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1829000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,228 +2600,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5121000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4983000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5114000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3411000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4702000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4722000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2573000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4884000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4766000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5018000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6698000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5024000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5315000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4711000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4737000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6554000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5949000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5378000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4718000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4504000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4839000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4287000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5217000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5337000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4074000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5160000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2065000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5062000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4246000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4666000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2022000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3736000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4478000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3553000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>4600000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>3747000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5003000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4879000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5005000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3306000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4593000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4602000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2705000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4762000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4648000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4909000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6577000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4900000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5199000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4580000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4613000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6407000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5800000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5245000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4588000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4357000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4700000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4156000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5095000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5194000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3944000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5032000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1939000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4924000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4120000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4545000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1908000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3620000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4362000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3450000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>4495000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2882,8 +2939,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2956,17 +3016,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2974,11 +3034,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>16761000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -2992,8 +3052,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3102,8 +3165,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3212,228 +3278,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-120000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-204000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-83000</v>
       </c>
-      <c r="G32" s="3">
-        <v>111000</v>
-      </c>
       <c r="H32" s="3">
+        <v>247000</v>
+      </c>
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-46000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-35000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-173000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-208000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-288000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-314000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-505000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1218000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-335000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-409000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-336000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-309000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-197000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-313000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-223000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-180000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-219000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-193000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-276000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-233000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-132000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-256000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-171000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-200000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-63000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-74000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5003000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4879000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5005000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3306000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4593000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4602000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2705000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4762000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4648000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4909000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6577000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4900000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5199000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4580000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4613000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6407000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5800000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5245000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4588000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4357000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4700000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4156000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5095000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5194000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3944000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5032000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1939000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4924000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4120000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4545000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>18669000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3620000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4362000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3450000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>4495000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3542,233 +3617,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5003000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4879000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5005000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3306000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4593000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4602000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2705000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4762000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4648000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4909000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6577000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4900000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5199000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4580000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4613000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6407000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5800000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5245000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4588000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4357000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4700000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4156000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5095000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5194000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3944000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5032000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1939000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4924000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4120000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4545000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>18669000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3620000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4362000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3450000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>4495000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3807,8 +3891,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3847,150 +3932,154 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3435000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2257000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4194000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4987000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2432000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2365000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2065000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4210000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4803000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2234000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2605000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2082000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1857000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1661000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2921000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9936000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4657000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10205000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>22171000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8983000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7882000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7047000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2594000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3020000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1949000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2322000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2745000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2538000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1750000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1923000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2079000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4487000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4583000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4307000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2880000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>6441000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E42" s="3">
         <v>27000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>26000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>55000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>60000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>100000</v>
-      </c>
-      <c r="K42" s="3">
-        <v>117000</v>
       </c>
       <c r="L42" s="3">
         <v>117000</v>
       </c>
       <c r="M42" s="3">
-        <v>0</v>
+        <v>117000</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -4067,778 +4156,802 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26812000</v>
+      </c>
+      <c r="E43" s="3">
         <v>26448000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>26109000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26523000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26155000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>25860000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>25085000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24143000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23728000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23436000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24506000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24362000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24606000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24335000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24585000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>22896000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>22029000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>23236000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>24650000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>23350000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>23434000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>24641000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>26277000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>25531000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>25738000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>25239000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>25859000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>24765000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>23875000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>22595000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>23493000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>21549000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>19771000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>16863000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>17513000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>14832000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2137000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2197000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2247000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2523000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1841000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2076000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2057000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2240000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1896000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2381000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2388000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3133000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3646000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3659000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3055000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2303000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1421000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1303000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1796000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1457000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1289000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1633000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1422000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1538000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1167000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1417000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1336000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1270000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1102000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1285000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1276000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1116000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1194000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1202000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1318000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4219000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4587000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5050000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2846000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4613000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4581000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4162000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2675000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4134000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4578000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8358000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10169000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7390000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5925000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6167000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5142000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7519000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4903000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5977000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4782000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4728000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7384000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7180000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4806000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4454000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4419000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4696000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4581000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4149000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5222000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3307000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3555000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3353000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4794000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>4800000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3030000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>38846000</v>
+      </c>
+      <c r="E46" s="3">
         <v>37353000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>40523000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>40641000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>38056000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37957000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>36814000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>38119000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>37388000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>35722000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>37857000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>39746000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>37499000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>35580000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>36728000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>40277000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>35626000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>39647000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>54594000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>38572000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>37333000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>40705000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>37473000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>34895000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>33308000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>33397000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>34636000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>33154000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>30876000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>31025000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>29913000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>30867000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>28823000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>27158000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>26395000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>25621000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1432000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1127000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1111000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1142000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1179000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1211000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1214000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1176000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1305000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1360000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1278000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1260000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1296000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1263000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1256000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1277000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>760000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>749000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>793000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>725000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>760000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>834000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>860000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>912000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>897000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>925000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>917000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>976000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1070000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>994000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1039000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1054000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1075000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1080000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1110000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1119000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>132018000</v>
+      </c>
+      <c r="E48" s="3">
         <v>132098000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>132994000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>131141000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>131954000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>132214000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>133036000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>132576000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>132615000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>132934000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>133564000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>129592000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>128408000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>127337000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>127579000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>123725000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>122382000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>117191000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>117364000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>115862000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>115185000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>114649000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>114609000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>111067000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>110285000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>110954000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>89286000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>87464000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>87781000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>87922000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>88568000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>86622000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>86521000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>85213000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>84751000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>83414000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>190296000</v>
+      </c>
+      <c r="E49" s="3">
         <v>190415000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>190583000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>189999000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>189813000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>189788000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>189567000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>195059000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>191081000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>190405000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>189928000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>189036000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>188648000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>188144000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>187899000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>177676000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>129951000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>132153000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>130283000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>130356000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>130034000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>126224000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>128946000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>128267000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>128439000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>128480000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>128519000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>132937000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>132916000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>132812000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>127836000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>127601000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>127674000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>124296000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>122775000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>121069000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4947,8 +5060,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5057,118 +5173,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3514000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2717000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2494000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2622000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2324000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2483000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2593000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2191000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2271000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2116000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17053000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15456000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14296000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13392000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13134000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10502000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>60471000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>55833000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>13447000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11479000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9947000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12088000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9839000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9734000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10179000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10191000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11471000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>11031000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10660000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11763000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9787000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8538000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8885000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>8984000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>9149000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>8275000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5277,118 +5399,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>383285000</v>
+      </c>
+      <c r="E54" s="3">
         <v>380364000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>384711000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>381164000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>379146000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>380158000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>380255000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>384830000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>379955000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>377716000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>379680000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>375090000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>370147000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>365716000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>366596000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>353457000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>349190000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>345573000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>316481000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>296994000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>293259000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>294500000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>291727000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>284875000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>283108000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>283947000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>264829000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>265562000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>263303000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>264516000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>257143000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>254682000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>252978000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>246731000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>244180000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>239498000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5427,8 +5555,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5467,668 +5596,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19880000</v>
+      </c>
+      <c r="E57" s="3">
         <v>19413000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10425000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22222000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19727000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>20139000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10021000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>26140000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>20067000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19273000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>23977000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>22235000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20956000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18169000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>24833000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20153000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17328000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>17219000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>20658000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>17391000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>19297000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>17419000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>21806000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>19566000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>17633000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>18664000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>22501000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>19342000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>18560000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>17052000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>21232000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>18434000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>17825000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>14826000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>13876000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>18002000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>28736000</v>
+      </c>
+      <c r="E58" s="3">
         <v>29248000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>27048000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>27776000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>29148000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21587000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17239000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>18067000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>19999000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17178000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9963000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14995000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12873000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13421000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7443000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7623000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7023000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>8802000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5889000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5770000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6651000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>11175000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>10777000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7830000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>8773000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>8614000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7190000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>6502000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>5466000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>6323000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3453000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2180000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1153000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3707000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2645000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3852000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12336000</v>
+      </c>
+      <c r="E59" s="3">
         <v>12405000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16251000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11818000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11931000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11905000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15143000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11470000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11338000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11317000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16231000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15911000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15395000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14995000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14884000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13582000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15727000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12709000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13113000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13024000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12938000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12463000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>12285000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11813000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>11808000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11329000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8239000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8323000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8303000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8240000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8352000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8316000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8780000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>8131000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>13819000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>8444000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>60952000</v>
+      </c>
+      <c r="E60" s="3">
         <v>61066000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>64771000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>61816000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>60806000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53631000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>53223000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>55677000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>51404000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>47768000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>50171000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>53141000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>49224000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>46585000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>47160000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>41358000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>40078000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>38730000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>39660000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>36185000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38886000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>41057000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>44868000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>39209000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>38214000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>38607000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>37930000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>34167000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>32329000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>31615000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>33037000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>28930000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>27758000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>26664000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>30340000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>30298000</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>146005000</v>
+      </c>
+      <c r="E61" s="3">
         <v>143285000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>144647000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>150580000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>149182000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>159187000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>161358000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>160007000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>162303000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>169023000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>140676000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>132912000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>136184000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>139961000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>143425000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>143352000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>144894000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>149700000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>123173000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>109790000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>106190000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>106561000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>100712000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>101769000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>104598000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>105045000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>105873000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>106440000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>109174000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>112734000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>113642000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>115317000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>116390000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>112839000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>105433000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>102739000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11981000</v>
+      </c>
+      <c r="E62" s="3">
         <v>13362000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13803000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10609000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10844000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10880000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10958000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11622000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11565000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8559000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>96370000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>100254000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>97382000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>93995000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>92811000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>90258000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>89106000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>84460000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>84376000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>84489000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>84070000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>85229000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>83312000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>83585000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>82349000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>82835000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>66316000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>68868000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>68225000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>67822000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>65777000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>81984000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>82069000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>82191000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>84375000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>84478000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6237,8 +6385,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6347,8 +6498,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6457,118 +6611,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>278924000</v>
+      </c>
+      <c r="E66" s="3">
         <v>278327000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>284136000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>283496000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>281607000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>284432000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>286456000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>285742000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>283453000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>283497000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>288536000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>287622000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>284131000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>281954000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>284806000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>276413000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>275506000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>274341000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>248639000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>231925000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>230562000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>234290000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>230332000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>225954000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>226526000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>228091000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>211684000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>211067000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>211279000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>213735000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>214047000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>227834000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>227789000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>223238000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>221656000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>219038000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6607,8 +6767,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6717,8 +6878,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6827,8 +6991,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6937,8 +7104,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7047,118 +7217,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>93275000</v>
+      </c>
+      <c r="E72" s="3">
         <v>91128000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>89110000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>86958000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>86504000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>84714000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>82915000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>88416000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>86448000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>84543000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>82380000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>78545000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>76401000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>73891000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>71993000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>70062000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>66310000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>63107000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>60464000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>58473000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>56746000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>54557000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>53147000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>50595000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>47945000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>46493000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>43542000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>44091000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>41657000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>39974000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>35635000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>19373000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>18159000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>16153000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>15059000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>12918000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7267,8 +7443,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7377,8 +7556,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7487,118 +7669,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>103063000</v>
+      </c>
+      <c r="E76" s="3">
         <v>100722000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>99237000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>96326000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>96172000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>94334000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>92430000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>97741000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>95193000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>92883000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>91144000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>87468000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>86016000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>83762000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>81790000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>77044000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>73684000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>71232000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>67842000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>65069000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>62697000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>60210000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>61395000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>58921000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>56582000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>55856000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>53145000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>54495000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>52024000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>50781000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>43096000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>26848000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>25189000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>23493000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>22524000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>20460000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7707,233 +7895,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5003000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4879000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5005000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3306000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4593000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4602000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2705000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4762000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4648000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4909000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6577000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4900000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5199000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4580000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4613000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6407000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5800000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5245000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4588000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4357000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4700000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4156000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5095000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5194000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3944000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5032000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1939000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4924000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4120000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4545000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>18669000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3620000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4362000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3450000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>4495000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7972,118 +8169,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3777000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3747000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4516000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3720000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3706000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3671000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3655000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3666000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3670000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3601000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4218000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4324000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4321000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4236000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4051000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3961000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4020000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4174000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4197000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4192000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4181000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4150000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4105000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4114000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4232000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4231000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4352000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4377000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4350000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4324000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4456000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4272000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>4167000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>4059000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>3987000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8192,8 +8393,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8302,8 +8506,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8412,8 +8619,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8522,8 +8732,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8632,118 +8845,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8975000</v>
+      </c>
+      <c r="E89" s="3">
         <v>7782000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10432000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9911000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9485000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7084000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8677000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10778000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9731000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8289000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8942000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10534000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10844000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6821000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8377000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10724000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>10744000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9694000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9296000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8920000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>14728000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8824000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8998000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>10912000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8755000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7081000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8095000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>9811000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>9785000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6648000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>8084000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>7303000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>8237000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1681000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>5086000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>4816000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8782,118 +9001,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3808000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4145000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5071000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3948000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3695000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4376000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4603000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4094000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4112000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5958000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8039000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5935000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5107000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7659000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6994000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6894000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4222000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4494000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4024000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4318000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4576000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5274000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5607000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4365000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3699000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4268000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4632000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4188000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3286000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4552000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-5965000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4271000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3944000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-6526000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-11570000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-8506000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9002,8 +9225,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9112,118 +9338,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3438000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3752000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5561000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4003000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3865000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5245000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7824000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5408000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4090000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6110000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5342000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8664000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6661000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7995000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10135000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2617000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4748000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-49653000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5043000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6345000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5144000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6980000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5424000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3568000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3786000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4803000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4798000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4408000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3443000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5285000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5469000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3728000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-4709000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4550000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-8444000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-5192000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9262,8 +9494,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9271,109 +9504,112 @@
         <v>2856000</v>
       </c>
       <c r="E96" s="3">
+        <v>2856000</v>
+      </c>
+      <c r="F96" s="3">
         <v>2850000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2801000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2802000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2796000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2794000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2744000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2743000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>2744000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2739000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2688000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2724000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2654000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2648000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2599000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2597000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2601000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2596000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2546000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2543000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2547000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-2542000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-2493000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-2492000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-2489000</v>
       </c>
       <c r="AC96" s="3">
         <v>-2489000</v>
       </c>
       <c r="AD96" s="3">
-        <v>-2438000</v>
+        <v>-2489000</v>
       </c>
       <c r="AE96" s="3">
         <v>-2438000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-2438000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-2407000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-2405000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-2357000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-2356000</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-2354000</v>
       </c>
       <c r="AK96" s="3">
         <v>-2354000</v>
       </c>
       <c r="AL96" s="3">
+        <v>-2354000</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-2303000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9482,8 +9718,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9592,8 +9831,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9702,118 +9944,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4378000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5893000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5623000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4415000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5634000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1428000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3016000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6055000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3203000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2383000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3076000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1616000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4082000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>245000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5192000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3081000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-11406000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>27956000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>9062000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1505000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-8795000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2563000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3863000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6258000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5386000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2657000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2956000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4556000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-6549000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3497000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2765000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>4665000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-203000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>3977000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9844,8 +10092,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9922,114 +10170,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1159000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1863000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-752000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1493000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>411000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2163000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-685000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2438000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-204000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>524000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>254000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>101000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-929000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6950000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5026000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5410000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-12003000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>13315000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1070000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>789000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4407000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-289000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1086000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-417000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-379000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>341000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>847000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-207000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>47000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2180000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-56000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>456000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1491000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>3584000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>VZ</t>
   </si>
@@ -656,491 +656,503 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>36381000</v>
+      </c>
+      <c r="E8" s="3">
         <v>33821000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>34504000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>33485000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>35681000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>33330000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32796000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32981000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>35130000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33336000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32596000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>32912000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>35251000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34241000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33789000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>33554000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34067000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>32915000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>33764000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>32867000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34692000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>31543000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>30447000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>31610000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>34775000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>32894000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>32071000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>32128000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>34281000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>32607000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>32203000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>31772000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>33955000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>31717000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>30548000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>29814000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>32340000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>30937000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>16273000</v>
+      </c>
+      <c r="E9" s="3">
         <v>13346000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13885000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13056000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15514000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13051000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12471000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12872000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15174000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13377000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12750000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13504000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15762000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14601000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14420000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14350000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14996000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13528000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14255000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13522000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14822000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12334000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>11749000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12296000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15631000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13384000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12721000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12990000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>15291000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>13331000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>13328000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>13255000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>15387000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>20614000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>12484000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>12047000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>14362000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>12229000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>20108000</v>
+      </c>
+      <c r="E10" s="3">
         <v>20475000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20619000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20429000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20167000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>20279000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>20325000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20109000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19956000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19959000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19846000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19408000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19489000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19640000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19369000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>19204000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19071000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19387000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19509000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19345000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19870000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19209000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>18698000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>19314000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>19144000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>19510000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>19350000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>19138000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>18990000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>19276000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>18875000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>18517000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>18568000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>11103000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>18064000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>17767000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>17978000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>18708000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1297,8 +1310,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1413,240 +1429,249 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2682000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-42000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-88000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-764000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2017000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>47000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>217000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7497000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>270000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>323000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-70000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-2214000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>645000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>198000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1241000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1230000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>948000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-168000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>223000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>404000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1092000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>255000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1377000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2381000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>291000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1544000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-96000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>4945000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>159000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>910000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>356000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>2558000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>620000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-1015000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>722000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>-1589000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>797000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4519000</v>
+      </c>
+      <c r="E15" s="3">
         <v>4618000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4635000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4387000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4506000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4458000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4483000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4224000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4516000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4410000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4359000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4318000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4218000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4324000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4321000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4236000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4051000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3961000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4020000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4174000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4197000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4192000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4181000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4150000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4105000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4114000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4232000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4231000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4350000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4370000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4338000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>4322000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>4237000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>8544000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>12388000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>8118000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>3987000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,240 +1709,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28745000</v>
+      </c>
+      <c r="E17" s="3">
         <v>25727000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>26470000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25223000</v>
       </c>
-      <c r="G17" s="3">
-        <v>28107000</v>
-      </c>
       <c r="H17" s="3">
+        <v>27835000</v>
+      </c>
+      <c r="I17" s="3">
         <v>25353000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25347000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25133000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27928000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25493000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24971000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25315000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25508000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26992000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26435000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26999000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>27689000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>24958000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25431000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25097000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>27695000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>24957000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>23341000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>25213000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>30127000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>25005000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>25765000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>24323000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>31991000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>24954000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>25586000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>24672000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>30058000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>25183000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>22534000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>23700000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>24317000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>24397000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7636000</v>
+      </c>
+      <c r="E18" s="3">
         <v>8094000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8034000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8262000</v>
       </c>
-      <c r="G18" s="3">
-        <v>7574000</v>
-      </c>
       <c r="H18" s="3">
+        <v>7846000</v>
+      </c>
+      <c r="I18" s="3">
         <v>7977000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7449000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7848000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7202000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7843000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7625000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7597000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9743000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7249000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7354000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6555000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6378000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7957000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8333000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7770000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6997000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6586000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>7106000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6397000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4648000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>7889000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>6306000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>7805000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2290000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>7653000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6617000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>7100000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3897000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>6534000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>8014000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>6114000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>8023000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>6540000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1958,588 +1990,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E20" s="3">
         <v>13000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-71000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>120000</v>
       </c>
-      <c r="G20" s="3">
-        <v>204000</v>
-      </c>
       <c r="H20" s="3">
+        <v>476000</v>
+      </c>
+      <c r="I20" s="3">
         <v>83000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-247000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>46000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>35000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>173000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>208000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>288000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>314000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>505000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1218000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>335000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>409000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>336000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>309000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>197000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>313000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>223000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>180000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>219000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>193000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>276000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>233000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>132000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>155000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>256000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>141000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>171000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>200000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>63000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11880000</v>
+      </c>
+      <c r="E21" s="3">
         <v>12699000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12740000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12529000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11876000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12352000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12179000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12073000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11706000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12207000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11987000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11880000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14134000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11781000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11963000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11105000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>10934000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>13136000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12688000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12353000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>11530000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>11087000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>11484000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>10860000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>8976000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>12183000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>10757000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>12229000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>6918000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>12263000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>11099000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>11579000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>8609000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>10947000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>12352000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>10373000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>12073000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>10556000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1759000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1664000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1639000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1632000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1644000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1672000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1698000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1635000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1599000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1433000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1285000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1207000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1105000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>937000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>785000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>786000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>739000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>801000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>844000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1101000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1080000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1044000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1116000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1034000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1159000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1146000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1215000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1210000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1199000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1211000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1222000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1201000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1219000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1164000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1218000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>1132000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>1137000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>1038000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3063000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6527000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6609000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6473000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6568000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4302000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6034000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6075000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1817000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6192000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6112000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6500000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8811000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6520000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6857000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6083000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6144000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8374000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7824000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7078000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6253000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5851000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6187000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5676000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3712000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6923000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5310000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6788000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1367000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>6675000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5527000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>6054000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2934000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5511000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>6967000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>5182000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>6949000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>5576000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>615000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1471000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1488000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1490000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1454000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>891000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1332000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1353000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>756000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1308000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1346000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1482000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2113000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1496000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1542000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1372000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1407000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1820000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1875000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1700000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1535000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1347000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1348000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1389000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1505000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1586000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1236000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1628000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-698000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1613000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1281000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1388000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>912000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1775000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>2489000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1629000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>2349000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1829000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2654,240 +2702,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2448000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5056000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5121000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4983000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5114000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3411000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4702000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4722000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2573000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4884000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4766000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5018000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6698000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5024000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5315000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4711000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4737000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6554000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5949000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5378000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4718000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4504000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4839000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4287000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5217000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5337000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4074000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5160000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2065000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5062000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4246000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4666000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2022000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3736000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>4478000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>3553000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>4600000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>3747000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2342000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4950000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5003000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4879000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5005000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3306000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4593000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4602000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2705000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4762000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4648000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4909000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6577000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4900000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5199000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4580000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4613000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6407000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5800000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5245000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4588000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4357000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4700000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4156000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5095000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5194000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3944000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5032000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1939000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4924000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4120000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4545000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1908000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3620000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>4362000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>3450000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>4495000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3002,8 +3059,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3082,17 +3142,17 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3100,11 +3160,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>16761000</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3118,8 +3178,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3234,8 +3297,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3350,240 +3416,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-275000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-13000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>71000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-120000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-204000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-476000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-83000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>247000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-46000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-35000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-173000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-208000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-288000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-314000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-505000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1218000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-335000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-409000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-336000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-309000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-197000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-313000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-223000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-180000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-219000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-193000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-276000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-233000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-132000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-256000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-171000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-200000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-63000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-74000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2342000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4950000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5003000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4879000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5005000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3306000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4593000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4602000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2705000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4762000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4648000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4909000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6577000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4900000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5199000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4580000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4613000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6407000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5800000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5245000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4588000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4357000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4700000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4156000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5095000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5194000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3944000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5032000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1939000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4924000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4120000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4545000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>18669000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3620000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>4362000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>3450000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>4495000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3698,245 +3773,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2342000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4950000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5003000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4879000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5005000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3306000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4593000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4602000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2705000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4762000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4648000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4909000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6577000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4900000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5199000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4580000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4613000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6407000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5800000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5245000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4588000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4357000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4700000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4156000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5095000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5194000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3944000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5032000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1939000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4924000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4120000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4545000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>18669000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3620000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>4362000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>3450000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>4495000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3977,8 +4061,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4019,162 +4104,166 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19048000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7706000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3435000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2257000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4194000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4987000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2432000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2365000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2065000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4210000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4803000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2234000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2605000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2082000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1857000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1661000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2921000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9936000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4657000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10205000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>22171000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8983000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7882000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7047000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2594000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3020000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1949000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2322000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2745000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2538000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1750000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1923000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2079000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4487000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4583000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4307000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2880000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>6441000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>32000</v>
       </c>
       <c r="F42" s="3">
+        <v>32000</v>
+      </c>
+      <c r="G42" s="3">
         <v>27000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>26000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>55000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>60000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>100000</v>
-      </c>
-      <c r="M42" s="3">
-        <v>117000</v>
       </c>
       <c r="N42" s="3">
         <v>117000</v>
       </c>
       <c r="O42" s="3">
-        <v>0</v>
+        <v>117000</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -4251,820 +4340,844 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27097000</v>
+      </c>
+      <c r="E43" s="3">
         <v>26469000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>26812000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26448000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26109000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>26523000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26155000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25860000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25085000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24143000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23728000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23436000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24506000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24362000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24606000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24335000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>24585000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>22896000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>22029000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>23236000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>24650000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>23350000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>23434000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>24641000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>26277000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>25531000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>25738000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>25239000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>25859000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>24765000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>23875000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>22595000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>23493000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>21549000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>19771000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>16863000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>17513000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>14832000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2441000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2700000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2137000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2197000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2247000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2523000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1841000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2076000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2057000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2240000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1896000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2381000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2388000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3133000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3646000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3659000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3055000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2303000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1421000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1303000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1796000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1457000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1289000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1633000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1422000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1538000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1167000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1417000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1336000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1270000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1102000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1285000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1276000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1116000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1194000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1202000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1318000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4389000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4248000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4219000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4587000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5050000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2846000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4613000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4581000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4162000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2675000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4134000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4578000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8358000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10169000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7390000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5925000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6167000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5142000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7519000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4903000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5977000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4782000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4728000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7384000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7180000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4806000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4454000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4419000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4696000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4581000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4149000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5222000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3307000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3555000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3353000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>4794000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>4800000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>3030000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>56922000</v>
+      </c>
+      <c r="E46" s="3">
         <v>44010000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>38846000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>37353000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>40523000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>40641000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>38056000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37957000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36814000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>38119000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>37388000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35722000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>37857000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>39746000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>37499000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>35580000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>36728000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>40277000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>35626000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>39647000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>54594000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>38572000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>37333000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>40705000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>37473000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>34895000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>33308000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>33397000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>34636000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>33154000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>30876000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>31025000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>29913000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>30867000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>28823000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>27158000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>26395000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>25621000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1412000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1432000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1127000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1111000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1142000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1179000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1211000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1214000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1176000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1305000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1360000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1278000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1260000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1296000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1263000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1256000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1277000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>760000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>749000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>793000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>725000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>760000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>834000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>860000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>912000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>897000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>925000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>917000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>976000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1070000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>994000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1039000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1054000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1075000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1080000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1110000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1119000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>132965000</v>
+      </c>
+      <c r="E48" s="3">
         <v>132227000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>132018000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>132098000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>132994000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>131141000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>131954000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>132214000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>133036000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>132576000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>132615000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>132934000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>133564000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>129592000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>128408000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>127337000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>127579000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>123725000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>122382000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>117191000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>117364000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>115862000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>115185000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>114649000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>114609000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>111067000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>110285000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>110954000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>89286000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>87464000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>87781000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>87922000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>88568000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>86622000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>86521000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>85213000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>84751000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>83414000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>190338000</v>
+      </c>
+      <c r="E49" s="3">
         <v>190283000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>190296000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>190415000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>190583000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>189999000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>189813000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>189788000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>189567000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>195059000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>191081000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>190405000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>189928000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>189036000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>188648000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>188144000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>187899000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>177676000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>129951000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>132153000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>130283000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>130356000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>130034000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>126224000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>128946000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>128267000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>128439000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>128480000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>128519000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>132937000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>132916000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>132812000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>127836000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>127601000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>127674000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>124296000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>122775000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>121069000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5179,8 +5292,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5295,124 +5411,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4251000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3261000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3514000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2717000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2494000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2622000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2324000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2483000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2593000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2191000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2271000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2116000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17053000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15456000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14296000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>13392000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>13134000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10502000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>60471000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>55833000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>13447000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11479000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9947000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>12088000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9839000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9734000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10179000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10191000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11471000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11031000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10660000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>11763000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9787000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>8538000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>8885000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>8984000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>9149000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>8275000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5527,124 +5649,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>404258000</v>
+      </c>
+      <c r="E54" s="3">
         <v>388331000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>383285000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>380364000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>384711000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>381164000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>379146000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>380158000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>380255000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>384830000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>379955000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>377716000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>379680000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>375090000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>370147000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>365716000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>366596000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>353457000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>349190000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>345573000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>316481000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>296994000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>293259000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>294500000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>291727000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>284875000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>283108000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>283947000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>264829000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>265562000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>263303000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>264516000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>257143000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>254682000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>252978000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>246731000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>244180000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>239498000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5685,8 +5813,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5727,704 +5856,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12154000</v>
+      </c>
+      <c r="E57" s="3">
         <v>20700000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19880000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19413000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10425000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22222000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19727000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>20139000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10021000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>26140000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>20067000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19273000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>23977000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22235000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>20956000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>18169000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>24833000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>20153000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17328000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>17219000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>20658000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>17391000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>19297000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>17419000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>21806000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>19566000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>17633000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>18664000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>22501000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>19342000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>18560000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>17052000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>21232000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>18434000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>17825000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>14826000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>13876000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>18002000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>23160000</v>
+      </c>
+      <c r="E58" s="3">
         <v>26621000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>28736000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>29248000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>27048000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>27776000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>29148000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21587000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17239000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>18067000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>19999000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>17178000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9963000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14995000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12873000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>13421000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7443000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>7623000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7023000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>8802000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5889000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5770000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6651000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>11175000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>10777000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7830000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>8773000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8614000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7190000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>6502000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>5466000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>6323000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3453000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2180000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1153000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3707000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>2645000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>3852000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16088000</v>
+      </c>
+      <c r="E59" s="3">
         <v>12242000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12336000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12405000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16251000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11818000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11931000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11905000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15143000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11470000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11338000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11317000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16231000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15911000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15395000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14995000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14884000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13582000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15727000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12709000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13113000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13024000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>12938000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12463000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12285000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11813000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11808000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11329000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8239000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8323000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8303000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8240000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8352000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>8316000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>8780000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>8131000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>13819000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>8444000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>62370000</v>
+      </c>
+      <c r="E60" s="3">
         <v>59563000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>60952000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>61066000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>64771000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>61816000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>60806000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>53631000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>53223000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>55677000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>51404000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>47768000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>50171000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>53141000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>49224000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>46585000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>47160000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>41358000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>40078000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38730000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>39660000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>36185000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>38886000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>41057000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>44868000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>39209000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>38214000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>38607000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>37930000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>34167000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>32329000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>31615000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>33037000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>28930000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>27758000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>26664000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>30340000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>30298000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>161654000</v>
+      </c>
+      <c r="E61" s="3">
         <v>148635000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>146005000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>143285000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>144647000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>150580000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>149182000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>159187000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>161358000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>160007000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>162303000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>169023000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>140676000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>132912000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>136184000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>139961000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>143425000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>143352000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>144894000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>149700000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>123173000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>109790000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>106190000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>106561000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>100712000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>101769000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>104598000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>105045000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>105873000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>106440000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>109174000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>112734000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>113642000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>115317000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>116390000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>112839000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>105433000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>102739000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12244000</v>
+      </c>
+      <c r="E62" s="3">
         <v>12253000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11981000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13362000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13803000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10609000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10844000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10880000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10958000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11622000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11565000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8559000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>96370000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>100254000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>97382000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>93995000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>92811000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>90258000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>89106000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>84460000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>84376000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>84489000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>84070000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>85229000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>83312000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>83585000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>82349000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>82835000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>66316000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>68868000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>68225000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>67822000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>65777000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>81984000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>82069000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>82191000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>84375000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>84478000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6539,8 +6687,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6655,8 +6806,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6771,124 +6925,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>298517000</v>
+      </c>
+      <c r="E66" s="3">
         <v>281986000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>278924000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>278327000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>284136000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>283496000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>281607000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>284432000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>286456000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>285742000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>283453000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>283497000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>288536000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>287622000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>284131000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>281954000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>284806000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>276413000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>275506000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>274341000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>248639000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>231925000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>230562000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>234290000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>230332000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>225954000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>226526000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>228091000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>211684000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>211067000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>211279000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>213735000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>214047000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>227834000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>227789000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>223238000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>221656000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>219038000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6929,8 +7089,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7045,8 +7206,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7161,8 +7325,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7277,8 +7444,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7393,124 +7563,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>94744000</v>
+      </c>
+      <c r="E72" s="3">
         <v>95316000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>93275000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>91128000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>89110000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>86958000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>86504000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>84714000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>82915000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>88416000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>86448000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>84543000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>82380000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>78545000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>76401000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>73891000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>71993000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>70062000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>66310000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>63107000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>60464000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>58473000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>56746000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>54557000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>53147000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>50595000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>47945000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>46493000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>43542000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>44091000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>41657000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>39974000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>35635000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>19373000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>18159000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>16153000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>15059000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>12918000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7625,8 +7801,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7741,8 +7920,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7857,124 +8039,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>104460000</v>
+      </c>
+      <c r="E76" s="3">
         <v>105042000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>103063000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>100722000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>99237000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>96326000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>96172000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>94334000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>92430000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>97741000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>95193000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>92883000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>91144000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>87468000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>86016000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>83762000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>81790000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>77044000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>73684000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>71232000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>67842000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>65069000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>62697000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>60210000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>61395000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>58921000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>56582000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>55856000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>53145000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>54495000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>52024000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>50781000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>43096000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>26848000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>25189000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>23493000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>22524000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>20460000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8089,245 +8277,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2342000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4950000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5003000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4879000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5005000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3306000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4593000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4602000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2705000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4762000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4648000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4909000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6577000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4900000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5199000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4580000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4613000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6407000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5800000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5245000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4588000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4357000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4700000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4156000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5095000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5194000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3944000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5032000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1939000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4924000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4120000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4545000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>18669000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3620000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>4362000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>3450000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>4495000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8368,124 +8565,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3805000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3782000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3777000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3747000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4516000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3720000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3706000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3671000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3655000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3666000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3670000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3601000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4218000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4324000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4321000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4236000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4051000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3961000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4020000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4174000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4197000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4192000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4181000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4150000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4105000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4114000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4232000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4231000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4352000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4377000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4350000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4324000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>4456000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>4272000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>4167000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>4059000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>3987000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8600,8 +8801,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8716,8 +8920,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8832,8 +9039,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8948,8 +9158,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9064,124 +9277,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9114000</v>
+      </c>
+      <c r="E89" s="3">
         <v>11266000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8975000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7782000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10432000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9911000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9485000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7084000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8677000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10778000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9731000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8289000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8942000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10534000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10844000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6821000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8377000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>10724000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10744000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9694000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9296000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8920000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>14728000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8824000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8998000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>10912000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8755000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7081000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>8095000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>9811000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>9785000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>6648000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>8084000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>7303000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>8237000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1681000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>5086000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>4816000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9222,124 +9441,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4748000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4310000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3808000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4145000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5071000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3948000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3695000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4376000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4603000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4094000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4112000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5958000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8039000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5935000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5107000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7659000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6994000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6894000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4222000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4494000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4024000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4318000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4576000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5274000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5607000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4365000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3699000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4268000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4632000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4188000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3286000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4552000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-5965000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-4271000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-3944000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-6526000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-11570000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-8506000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9454,8 +9677,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9570,124 +9796,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4980000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4490000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3438000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3752000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5561000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4003000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3865000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5245000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7824000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5408000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4090000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6110000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5342000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8664000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6661000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7995000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10135000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2617000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4748000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-49653000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5043000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6345000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5144000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6980000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5424000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3568000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3786000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4803000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4798000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4408000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3443000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-5285000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5469000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3728000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-4709000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-4550000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-8444000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-5192000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9728,124 +9960,128 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2912000</v>
+      </c>
+      <c r="E96" s="3">
         <v>2857000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>2856000</v>
       </c>
       <c r="F96" s="3">
         <v>2856000</v>
       </c>
       <c r="G96" s="3">
+        <v>2856000</v>
+      </c>
+      <c r="H96" s="3">
         <v>2850000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2801000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2802000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2796000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2794000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>2744000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>2743000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>2744000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2739000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2688000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2724000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2654000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2648000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2599000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2597000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2601000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2596000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2546000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-2543000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-2547000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-2542000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-2493000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-2492000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-2489000</v>
       </c>
       <c r="AE96" s="3">
         <v>-2489000</v>
       </c>
       <c r="AF96" s="3">
-        <v>-2438000</v>
+        <v>-2489000</v>
       </c>
       <c r="AG96" s="3">
         <v>-2438000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-2438000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-2407000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-2405000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-2357000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-2356000</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-2354000</v>
       </c>
       <c r="AM96" s="3">
         <v>-2354000</v>
       </c>
       <c r="AN96" s="3">
+        <v>-2354000</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-2303000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9960,8 +10196,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10076,8 +10315,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10192,124 +10434,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7209000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2551000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4378000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5893000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5623000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4415000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5634000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1428000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3016000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6055000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3203000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2383000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3076000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1616000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4082000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>245000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5192000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3081000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-11406000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>27956000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>9062000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1505000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-8795000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2563000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3863000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-6258000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5386000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2657000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2956000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4556000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-6549000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-3497000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2765000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>4665000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-203000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>3977000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10346,8 +10594,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10424,120 +10672,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11343000</v>
+      </c>
+      <c r="E102" s="3">
         <v>4225000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1159000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1863000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-752000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1493000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>411000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2163000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-685000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2438000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-204000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>524000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>254000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>101000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-929000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6950000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5026000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5410000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-12003000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13315000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1070000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>789000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4407000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-289000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1086000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-417000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-379000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>341000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>847000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-207000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>47000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2180000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-56000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>456000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1491000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>3584000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>VZ</t>
   </si>
@@ -656,503 +656,515 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>34440000</v>
+      </c>
+      <c r="E8" s="3">
         <v>36381000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33821000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>34504000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>33485000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>35681000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33330000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32796000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>32981000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>35130000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33336000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>32596000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32912000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>35251000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34241000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>33789000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>33554000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34067000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>32915000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>33764000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>32867000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>34692000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>31543000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>30447000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>31610000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>34775000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>32894000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>32071000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>32128000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>34281000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>32607000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>32203000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>31772000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>33955000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>31717000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>30548000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>29814000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>32340000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>30937000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13673000</v>
+      </c>
+      <c r="E9" s="3">
         <v>16273000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13346000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13885000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13056000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15514000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13051000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12471000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12872000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15174000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13377000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12750000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13504000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15762000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14601000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14420000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14350000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14996000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13528000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14255000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13522000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14822000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12334000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>11749000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12296000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15631000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13384000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12721000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12990000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>15291000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>13331000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>13328000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>13255000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>15387000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>20614000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>12484000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>12047000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>14362000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>12229000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>20767000</v>
+      </c>
+      <c r="E10" s="3">
         <v>20108000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20475000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20619000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20429000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>20167000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>20279000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20325000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>20109000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19956000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19959000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19846000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19408000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19489000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19640000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>19369000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19204000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19071000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19387000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19509000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19345000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19870000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19209000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>18698000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>19314000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>19144000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>19510000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>19350000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>19138000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>18990000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>19276000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>18875000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>18517000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>18568000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>11103000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>18064000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>17767000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>17978000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>18708000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,8 +1206,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1313,8 +1326,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,246 +1448,255 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2682000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-42000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-88000</v>
       </c>
-      <c r="G14" s="3">
-        <v>100000</v>
-      </c>
       <c r="H14" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-764000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2017000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>47000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>217000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7497000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>270000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>323000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-70000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-2214000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>645000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>198000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1241000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1230000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>948000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-168000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>223000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>404000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1092000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>255000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1377000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2381000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>291000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1544000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-96000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>4945000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>159000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>910000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>356000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>2558000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>620000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-1015000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>722000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>-1589000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>797000</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4892000</v>
+      </c>
+      <c r="E15" s="3">
         <v>4519000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4618000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4635000</v>
       </c>
-      <c r="G15" s="3">
-        <v>4387000</v>
-      </c>
       <c r="H15" s="3">
+        <v>4577000</v>
+      </c>
+      <c r="I15" s="3">
         <v>4506000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4458000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4483000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4224000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4516000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4410000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4359000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4318000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4218000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4324000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4321000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4236000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4051000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3961000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4020000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4174000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4197000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4192000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4181000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4150000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4105000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4114000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4232000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>4231000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4350000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4370000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>4338000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>4322000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>4237000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>8544000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>12388000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>8118000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>3987000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1735,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25766000</v>
+      </c>
+      <c r="E17" s="3">
         <v>28745000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25727000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>26470000</v>
       </c>
-      <c r="G17" s="3">
-        <v>25223000</v>
-      </c>
       <c r="H17" s="3">
+        <v>25601000</v>
+      </c>
+      <c r="I17" s="3">
         <v>27835000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25353000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25347000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25133000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27928000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25493000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24971000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25315000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25508000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26992000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26435000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26999000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>27689000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>24958000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25431000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>25097000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>27695000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>24957000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>23341000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>25213000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>30127000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>25005000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>25765000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>24323000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>31991000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>24954000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>25586000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>24672000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>30058000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>25183000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>22534000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>23700000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>24317000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>24397000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8674000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7636000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8094000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8034000</v>
       </c>
-      <c r="G18" s="3">
-        <v>8262000</v>
-      </c>
       <c r="H18" s="3">
+        <v>7884000</v>
+      </c>
+      <c r="I18" s="3">
         <v>7846000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7977000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7449000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7848000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7202000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7843000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7625000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7597000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9743000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7249000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7354000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6555000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6378000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7957000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8333000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7770000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6997000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6586000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7106000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6397000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4648000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>7889000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>6306000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>7805000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2290000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>7653000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>6617000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>7100000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3897000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>6534000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>8014000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>6114000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>8023000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>6540000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,603 +2023,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="E20" s="3">
         <v>275000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>13000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-71000</v>
       </c>
-      <c r="G20" s="3">
-        <v>120000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-68000</v>
+      </c>
+      <c r="I20" s="3">
         <v>476000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>83000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-247000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>46000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>35000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>173000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>208000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>288000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>314000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>505000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1218000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>335000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>409000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>336000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>309000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>197000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>313000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>223000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>180000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>219000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>193000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>276000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>233000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>132000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>155000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>256000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>141000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>171000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>200000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>63000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13635000</v>
+      </c>
+      <c r="E21" s="3">
         <v>11880000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12699000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12740000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12529000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11876000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12352000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12179000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12073000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11706000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12207000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11987000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11880000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14134000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11781000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11963000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11105000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10934000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>13136000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12688000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>12353000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>11530000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>11087000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11484000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>10860000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>8976000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>12183000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>10757000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>12229000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6918000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>12263000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>11099000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>11579000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>8609000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>10947000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>12352000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>10373000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>12073000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>10556000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1940000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1759000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1664000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1639000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1632000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1644000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1672000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1698000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1635000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1599000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1433000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1285000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1207000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1105000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>937000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>785000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>786000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>739000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>801000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>844000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1101000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1080000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1044000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1116000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1034000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1159000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1146000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1215000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1210000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1199000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1211000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1222000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1201000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1219000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1164000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>1218000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>1132000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>1137000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>1038000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6784000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3063000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6527000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6609000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6473000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6568000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4302000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6034000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6075000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1817000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6192000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6112000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6500000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8811000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6520000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6857000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6083000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6144000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8374000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7824000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>7078000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6253000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5851000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6187000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5676000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3712000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6923000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5310000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6788000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1367000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>6675000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5527000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>6054000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2934000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>5511000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>6967000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>5182000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>6949000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>5576000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1638000</v>
+      </c>
+      <c r="E24" s="3">
         <v>615000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1471000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1488000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1490000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1454000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>891000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1332000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1353000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>756000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1308000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1346000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1482000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2113000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1496000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1542000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1372000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1407000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1820000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1875000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1700000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1535000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1347000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1348000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1389000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1505000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1586000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1236000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1628000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-698000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1613000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1281000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1388000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>912000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1775000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>2489000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1629000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>2349000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1829000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2753,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5146000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2448000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5056000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5121000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4983000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5114000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3411000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4702000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4722000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2573000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4884000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4766000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5018000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6698000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5024000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5315000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4711000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4737000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6554000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5949000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5378000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4718000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4504000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4839000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4287000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5217000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5337000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4074000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5160000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2065000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5062000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4246000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4666000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2022000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3736000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>4478000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>3553000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>4600000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>3747000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5045000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2342000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4950000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5003000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4879000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5005000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3306000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4593000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4602000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2705000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4762000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4648000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4909000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6577000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4900000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5199000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4580000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4613000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6407000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5800000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5245000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4588000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4357000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4700000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4156000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5095000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5194000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3944000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5032000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1939000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4924000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4120000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4545000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1908000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3620000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>4362000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>3450000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>4495000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3119,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,17 +3205,17 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AF29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3163,11 +3223,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>16761000</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3181,8 +3241,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3363,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,246 +3485,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-275000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-13000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>71000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-120000</v>
-      </c>
       <c r="H32" s="3">
+        <v>68000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-476000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-83000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>247000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-46000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-35000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-173000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-208000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-288000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-314000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-505000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1218000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-335000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-409000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-336000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-309000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-197000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-313000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-223000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-180000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-219000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-193000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-276000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-233000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-132000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-256000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-171000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-200000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-63000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-74000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5045000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2342000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4950000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5003000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4879000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5005000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3306000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4593000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4602000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2705000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4762000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4648000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4909000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6577000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4900000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5199000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4580000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4613000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6407000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5800000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5245000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4588000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4357000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4700000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4156000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5095000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5194000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3944000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5032000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1939000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4924000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4120000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4545000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>18669000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3620000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>4362000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>3450000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>4495000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3851,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5045000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2342000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4950000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5003000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4879000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5005000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3306000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4593000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4602000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2705000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4762000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4648000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4909000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6577000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4900000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5199000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4580000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4613000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6407000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5800000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5245000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4588000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4357000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4700000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4156000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5095000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5194000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3944000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5032000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1939000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4924000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4120000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4545000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>18669000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3620000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>4362000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>3450000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>4495000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4146,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,168 +4190,172 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8366000</v>
+      </c>
+      <c r="E41" s="3">
         <v>19048000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7706000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3435000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2257000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4194000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4987000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2432000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2365000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2065000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4210000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4803000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2234000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2605000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2082000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1857000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1661000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2921000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9936000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4657000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10205000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>22171000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8983000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7882000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7047000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2594000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3020000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1949000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2322000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2745000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2538000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1750000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1923000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2079000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4487000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4583000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4307000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2880000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>6441000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="E42" s="3">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>32000</v>
       </c>
       <c r="G42" s="3">
+        <v>32000</v>
+      </c>
+      <c r="H42" s="3">
         <v>27000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>26000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>55000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>60000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>100000</v>
-      </c>
-      <c r="N42" s="3">
-        <v>117000</v>
       </c>
       <c r="O42" s="3">
         <v>117000</v>
       </c>
       <c r="P42" s="3">
-        <v>0</v>
+        <v>117000</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -4343,841 +4432,865 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27105000</v>
+      </c>
+      <c r="E43" s="3">
         <v>27097000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>26469000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26812000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26448000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>26109000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26523000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>26155000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25860000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>25085000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24143000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23728000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>23436000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24506000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24362000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24606000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>24335000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>24585000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>22896000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>22029000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>23236000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>24650000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>23350000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>23434000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>24641000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>26277000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>25531000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>25738000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>25239000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>25859000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>24765000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>23875000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>22595000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>23493000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>21549000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>19771000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>16863000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>17513000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>14832000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2320000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2441000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2700000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2137000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2197000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2247000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2523000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1841000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2076000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2057000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2240000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1896000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2381000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2388000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3133000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3646000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3659000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3055000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2303000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1421000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1303000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1796000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1457000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1289000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1633000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1422000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1538000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1167000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1417000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1336000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1270000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1102000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1285000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1276000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1116000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1194000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1202000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1318000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4512000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4389000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4248000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4219000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4587000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5050000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2846000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4613000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4581000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4162000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2675000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4134000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4578000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8358000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10169000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7390000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5925000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6167000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5142000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7519000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4903000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5977000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4782000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4728000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7384000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7180000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4806000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4454000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4419000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4696000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4581000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4149000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5222000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3307000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3555000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3353000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>4794000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>4800000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>3030000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>44723000</v>
+      </c>
+      <c r="E46" s="3">
         <v>56922000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>44010000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38846000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>37353000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>40523000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>40641000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>38056000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>37957000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36814000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>38119000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>37388000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>35722000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>37857000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>39746000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>37499000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>35580000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>36728000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>40277000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>35626000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>39647000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>54594000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>38572000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>37333000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>40705000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>37473000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>34895000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>33308000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>33397000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>34636000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>33154000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>30876000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>31025000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>29913000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>30867000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>28823000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>27158000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>26395000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>25621000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1591000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1129000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1412000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1432000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1127000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1111000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1142000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1179000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1211000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1214000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1176000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1305000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1360000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1278000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1260000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1296000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1263000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1256000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1277000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>760000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>749000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>793000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>725000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>760000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>834000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>860000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>912000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>897000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>925000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>917000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>976000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1070000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>994000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1039000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1054000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1075000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1080000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1110000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1119000</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>149373000</v>
+      </c>
+      <c r="E48" s="3">
         <v>132965000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>132227000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>132018000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>132098000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>132994000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>131141000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>131954000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>132214000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>133036000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>132576000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>132615000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>132934000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>133564000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>129592000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>128408000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>127337000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>127579000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>123725000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>122382000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>117191000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>117364000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>115862000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>115185000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>114649000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>114609000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>111067000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>110285000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>110954000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>89286000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>87464000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>87781000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>87922000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>88568000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>86622000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>86521000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>85213000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>84751000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>83414000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>200509000</v>
+      </c>
+      <c r="E49" s="3">
         <v>190338000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>190283000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>190296000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>190415000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>190583000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>189999000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>189813000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>189788000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>189567000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>195059000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>191081000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>190405000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>189928000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>189036000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>188648000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>188144000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>187899000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>177676000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>129951000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>132153000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>130283000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>130356000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>130034000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>126224000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>128946000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>128267000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>128439000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>128480000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>128519000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>132937000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>132916000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>132812000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>127836000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>127601000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>127674000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>124296000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>122775000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>121069000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5408,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,127 +5530,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3400000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4251000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3261000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3514000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2717000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2494000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2622000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2324000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2483000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2593000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2191000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2271000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2116000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>17053000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15456000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14296000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>13392000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>13134000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10502000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>60471000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>55833000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>13447000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11479000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9947000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>12088000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9839000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9734000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10179000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10191000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11471000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>11031000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10660000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>11763000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9787000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>8538000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>8885000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>8984000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>9149000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>8275000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5774,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>417882000</v>
+      </c>
+      <c r="E54" s="3">
         <v>404258000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>388331000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>383285000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>380364000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>384711000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>381164000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>379146000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>380158000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>380255000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>384830000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>379955000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>377716000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>379680000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>375090000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>370147000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>365716000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>366596000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>353457000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>349190000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>345573000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>316481000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>296994000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>293259000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>294500000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>291727000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>284875000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>283108000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>283947000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>264829000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>265562000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>263303000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>264516000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>257143000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>254682000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>252978000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>246731000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>244180000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>239498000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +5942,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,722 +5986,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21932000</v>
+      </c>
+      <c r="E57" s="3">
         <v>12154000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20700000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19880000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19413000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10425000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22222000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19727000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>20139000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10021000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>26140000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>20067000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19273000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>23977000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>22235000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20956000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>18169000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>24833000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>20153000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>17328000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>17219000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>20658000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>17391000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>19297000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>17419000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>21806000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>19566000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>17633000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>18664000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>22501000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>19342000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>18560000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>17052000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>21232000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>18434000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>17825000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>14826000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>13876000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>18002000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>35099000</v>
+      </c>
+      <c r="E58" s="3">
         <v>23160000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>26621000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>28736000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>29248000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>27048000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>27776000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>29148000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21587000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17239000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>18067000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>19999000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>17178000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9963000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14995000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>12873000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>13421000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>7443000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7623000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7023000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>8802000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5889000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5770000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6651000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>11175000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>10777000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7830000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8773000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>8614000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7190000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>6502000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>5466000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>6323000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3453000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2180000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1153000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3707000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>2645000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>3852000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12849000</v>
+      </c>
+      <c r="E59" s="3">
         <v>16088000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12242000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12336000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12405000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16251000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11818000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11931000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11905000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15143000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11470000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11338000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11317000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16231000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15911000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15395000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14995000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14884000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13582000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15727000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12709000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13113000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13024000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12938000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12463000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>12285000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11813000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11808000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11329000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8239000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8323000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8303000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8240000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>8352000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>8316000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>8780000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>8131000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>13819000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>8444000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>69880000</v>
+      </c>
+      <c r="E60" s="3">
         <v>62370000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>59563000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>60952000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>61066000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>64771000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>61816000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>60806000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>53631000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>53223000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>55677000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>51404000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>47768000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>50171000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>53141000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>49224000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>46585000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>47160000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>41358000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>40078000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38730000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>39660000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>36185000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>38886000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>41057000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>44868000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>39209000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>38214000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>38607000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>37930000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>34167000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>32329000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>31615000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>33037000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>28930000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>27758000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>26664000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>30340000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>30298000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>165822000</v>
+      </c>
+      <c r="E61" s="3">
         <v>161654000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>148635000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>146005000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>143285000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>144647000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>150580000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>149182000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>159187000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>161358000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>160007000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>162303000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>169023000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>140676000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>132912000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>136184000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>139961000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>143425000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>143352000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>144894000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>149700000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>123173000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>109790000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>106190000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>106561000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>100712000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>101769000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>104598000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>105045000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>105873000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>106440000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>109174000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>112734000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>113642000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>115317000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>116390000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>112839000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>105433000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>102739000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13617000</v>
+      </c>
+      <c r="E62" s="3">
         <v>12244000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12253000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11981000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13362000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13803000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10609000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10844000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10880000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10958000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11622000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11565000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8559000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>96370000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>100254000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>97382000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>93995000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>92811000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>90258000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>89106000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>84460000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>84376000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>84489000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>84070000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>85229000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>83312000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>83585000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>82349000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>82835000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>66316000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>68868000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>68225000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>67822000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>65777000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>81984000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>82069000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>82191000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>84375000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>84478000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6838,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +6960,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7082,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>313260000</v>
+      </c>
+      <c r="E66" s="3">
         <v>298517000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>281986000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>278924000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>278327000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>284136000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>283496000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>281607000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>284432000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>286456000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>285742000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>283453000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>283497000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>288536000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>287622000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>284131000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>281954000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>284806000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>276413000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>275506000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>274341000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>248639000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>231925000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>230562000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>234290000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>230332000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>225954000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>226526000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>228091000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>211684000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>211067000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>211279000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>213735000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>214047000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>227834000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>227789000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>223238000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>221656000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>219038000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7250,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7370,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,8 +7492,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7447,8 +7614,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7736,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>96824000</v>
+      </c>
+      <c r="E72" s="3">
         <v>94744000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>95316000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>93275000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>91128000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>89110000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>86958000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>86504000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>84714000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>82915000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>88416000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>86448000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>84543000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>82380000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>78545000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>76401000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>73891000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>71993000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>70062000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>66310000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>63107000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>60464000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>58473000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>56746000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>54557000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>53147000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>50595000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>47945000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>46493000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>43542000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>44091000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>41657000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>39974000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>35635000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>19373000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>18159000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>16153000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>15059000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>12918000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +7980,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8102,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8224,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>103309000</v>
+      </c>
+      <c r="E76" s="3">
         <v>104460000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>105042000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>103063000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>100722000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>99237000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>96326000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>96172000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>94334000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>92430000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>97741000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>95193000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>92883000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>91144000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>87468000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>86016000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>83762000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>81790000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>77044000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>73684000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>71232000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>67842000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>65069000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>62697000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>60210000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>61395000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>58921000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>56582000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>55856000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>53145000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>54495000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>52024000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>50781000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>43096000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>26848000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>25189000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>23493000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>22524000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>20460000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8468,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5045000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2342000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4950000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5003000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4879000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5005000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3306000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4593000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4602000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2705000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4762000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4648000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4909000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6577000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4900000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5199000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4580000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4613000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6407000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5800000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5245000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4588000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4357000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4700000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4156000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5095000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5194000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3944000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5032000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1939000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4924000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4120000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4545000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>18669000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3620000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>4362000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>3450000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>4495000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>3620000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,127 +8763,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3843000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3805000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3782000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3777000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3747000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4516000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3720000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3706000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3671000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3655000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3666000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3670000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3601000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4218000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4324000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4321000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4236000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4051000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3961000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4020000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4174000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4197000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4192000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4181000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4150000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4105000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4114000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4232000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4231000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4352000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4377000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4350000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>4324000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>4456000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>4272000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>4167000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>4059000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>3987000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>3942000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9005,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9127,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9249,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9371,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,127 +9493,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7984000</v>
+      </c>
+      <c r="E89" s="3">
         <v>9114000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11266000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8975000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7782000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10432000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9911000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9485000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7084000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8677000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10778000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9731000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8289000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8942000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10534000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10844000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6821000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8377000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10724000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>10744000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9694000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9296000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8920000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>14728000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8824000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8998000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>10912000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8755000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7081000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>8095000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>9811000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>9785000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>6648000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>8084000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>7303000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>8237000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1681000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>5086000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>4816000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,127 +9661,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4201000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4748000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4310000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3808000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4145000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5071000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3948000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3695000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4376000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4603000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4094000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4112000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5958000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8039000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5935000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5107000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7659000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6994000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6894000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4222000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4494000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4024000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4318000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4576000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5274000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5607000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4365000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3699000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4268000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4632000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4188000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3286000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4552000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-5965000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-4271000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-3944000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-6526000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-11570000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-8506000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +9903,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,127 +10025,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13573000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4980000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4490000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3438000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3752000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5561000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4003000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3865000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5245000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7824000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5408000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4090000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6110000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5342000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8664000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6661000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7995000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10135000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2617000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4748000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-49653000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5043000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6345000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5144000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6980000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5424000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3568000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3786000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4803000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4798000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4408000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3443000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5285000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-5469000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3728000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-4709000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-4550000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-8444000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-5192000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,127 +10193,131 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2910000</v>
+      </c>
+      <c r="E96" s="3">
         <v>2912000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2857000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>2856000</v>
       </c>
       <c r="G96" s="3">
         <v>2856000</v>
       </c>
       <c r="H96" s="3">
+        <v>2856000</v>
+      </c>
+      <c r="I96" s="3">
         <v>2850000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2801000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2802000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2796000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>2794000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>2744000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>2743000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>2744000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2739000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2688000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2724000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2654000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2648000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2599000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2597000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2601000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2596000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-2546000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-2543000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-2547000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-2542000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-2493000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-2492000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-2489000</v>
       </c>
       <c r="AF96" s="3">
         <v>-2489000</v>
       </c>
       <c r="AG96" s="3">
-        <v>-2438000</v>
+        <v>-2489000</v>
       </c>
       <c r="AH96" s="3">
         <v>-2438000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-2438000</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-2407000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-2405000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-2357000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-2356000</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-2354000</v>
       </c>
       <c r="AN96" s="3">
         <v>-2354000</v>
       </c>
       <c r="AO96" s="3">
+        <v>-2354000</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-2303000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10435,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10557,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,127 +10679,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5278000</v>
+      </c>
+      <c r="E100" s="3">
         <v>7209000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2551000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4378000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5893000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5623000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4415000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5634000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1428000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3016000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6055000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3203000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2383000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3076000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1616000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4082000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>245000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5192000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3081000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-11406000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>27956000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>9062000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1505000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-8795000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2563000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3863000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-6258000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5386000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2657000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2956000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4556000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-6549000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-4554000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-3497000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2765000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>4665000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-203000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>3977000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10597,8 +10845,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10675,123 +10923,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10867000</v>
+      </c>
+      <c r="E102" s="3">
         <v>11343000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4225000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1159000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1863000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-752000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1493000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>411000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2163000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-685000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2438000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-204000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>524000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>254000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>101000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-929000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6950000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5026000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5410000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-12003000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>13315000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1070000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>789000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4407000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-289000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1086000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-417000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-379000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>341000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>847000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-207000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>47000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2180000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-56000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>456000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>1491000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-3561000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>3584000</v>
       </c>
     </row>
